--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="125">
   <si>
     <t>MÊS</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>PROINSU CE 220826</t>
+  </si>
+  <si>
+    <t>PROINSU SAN 220826</t>
   </si>
   <si>
     <t>Setembro</t>
@@ -504,7 +507,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -536,6 +539,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -665,7 +673,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -696,23 +704,20 @@
     <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -723,8 +728,29 @@
     <xf borderId="9" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="6" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1090,7 +1116,7 @@
       <c r="B4" s="6">
         <v>6.0</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="7" t="s">
@@ -1392,7 +1418,7 @@
       <c r="B11" s="6">
         <v>20.0</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="7" t="s">
@@ -1606,7 +1632,7 @@
       <c r="B16" s="6">
         <v>3.0</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="7" t="s">
@@ -1910,7 +1936,7 @@
       <c r="B23" s="6">
         <v>17.0</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="7" t="s">
@@ -2175,7 +2201,7 @@
       <c r="A32" s="5"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="11"/>
+      <c r="D32" s="10"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
@@ -2515,7 +2541,7 @@
       <c r="A41" s="5"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
-      <c r="D41" s="11"/>
+      <c r="D41" s="10"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
@@ -3055,7 +3081,7 @@
       <c r="A56" s="5"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
-      <c r="D56" s="11"/>
+      <c r="D56" s="10"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
@@ -3395,7 +3421,7 @@
       <c r="A65" s="5"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
-      <c r="D65" s="11"/>
+      <c r="D65" s="10"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
@@ -3651,7 +3677,7 @@
       <c r="A72" s="5"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
-      <c r="D72" s="11"/>
+      <c r="D72" s="10"/>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
@@ -4077,7 +4103,7 @@
       <c r="A83" s="5"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
-      <c r="D83" s="11"/>
+      <c r="D83" s="10"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
@@ -4451,7 +4477,7 @@
       <c r="C92" s="8"/>
       <c r="D92" s="7"/>
       <c r="E92" s="6"/>
-      <c r="F92" s="12"/>
+      <c r="F92" s="11"/>
       <c r="G92" s="6"/>
       <c r="H92" s="6"/>
       <c r="I92" s="8"/>
@@ -4479,7 +4505,7 @@
       <c r="C93" s="8"/>
       <c r="D93" s="7"/>
       <c r="E93" s="6"/>
-      <c r="F93" s="12"/>
+      <c r="F93" s="11"/>
       <c r="G93" s="6"/>
       <c r="H93" s="6"/>
       <c r="I93" s="8"/>
@@ -4505,7 +4531,7 @@
       <c r="A94" s="5"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
-      <c r="D94" s="11"/>
+      <c r="D94" s="10"/>
       <c r="E94" s="8"/>
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
@@ -5077,7 +5103,7 @@
       <c r="A109" s="5"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
-      <c r="D109" s="11"/>
+      <c r="D109" s="10"/>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
@@ -5381,7 +5407,7 @@
       <c r="A117" s="5"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
-      <c r="D117" s="11"/>
+      <c r="D117" s="10"/>
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
@@ -5685,7 +5711,7 @@
       <c r="A125" s="5"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
-      <c r="D125" s="11"/>
+      <c r="D125" s="10"/>
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
       <c r="G125" s="8"/>
@@ -5945,7 +5971,7 @@
       <c r="A132" s="5"/>
       <c r="B132" s="6"/>
       <c r="C132" s="8"/>
-      <c r="D132" s="11"/>
+      <c r="D132" s="10"/>
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
       <c r="G132" s="8"/>
@@ -6061,7 +6087,7 @@
       <c r="A135" s="5"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
-      <c r="D135" s="11"/>
+      <c r="D135" s="10"/>
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
@@ -6177,7 +6203,7 @@
       <c r="A138" s="5"/>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
-      <c r="D138" s="11"/>
+      <c r="D138" s="10"/>
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
       <c r="G138" s="8"/>
@@ -6203,28 +6229,28 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B139" s="6">
+        <v>22.0</v>
+      </c>
+      <c r="C139" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B139" s="13">
-        <v>7.0</v>
-      </c>
-      <c r="C139" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D139" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E139" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F139" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G139" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H139" s="13" t="s">
-        <v>46</v>
+      <c r="D139" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H139" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="I139" s="8"/>
       <c r="J139" s="8"/>
@@ -6247,28 +6273,28 @@
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B140" s="6">
+        <v>23.0</v>
+      </c>
+      <c r="C140" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B140" s="13">
-        <v>21.0</v>
-      </c>
-      <c r="C140" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D140" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E140" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F140" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G140" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H140" s="13" t="s">
-        <v>46</v>
+      <c r="D140" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H140" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="I140" s="8"/>
       <c r="J140" s="8"/>
@@ -6293,7 +6319,7 @@
       <c r="A141" s="5"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
-      <c r="D141" s="11"/>
+      <c r="D141" s="10"/>
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
       <c r="G141" s="8"/>
@@ -6319,28 +6345,28 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B142" s="13">
         <v>7.0</v>
       </c>
       <c r="C142" s="13" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F142" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="I142" s="8"/>
       <c r="J142" s="8"/>
@@ -6363,28 +6389,28 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B143" s="13">
         <v>21.0</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F143" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H143" s="13" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="I143" s="8"/>
       <c r="J143" s="8"/>
@@ -6406,30 +6432,14 @@
       <c r="Z143" s="9"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B144" s="13">
-        <v>7.0</v>
-      </c>
-      <c r="C144" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E144" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F144" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G144" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H144" s="13" t="s">
-        <v>17</v>
-      </c>
+      <c r="A144" s="5"/>
+      <c r="B144" s="8"/>
+      <c r="C144" s="8"/>
+      <c r="D144" s="10"/>
+      <c r="E144" s="8"/>
+      <c r="F144" s="8"/>
+      <c r="G144" s="8"/>
+      <c r="H144" s="8"/>
       <c r="I144" s="8"/>
       <c r="J144" s="8"/>
       <c r="K144" s="8"/>
@@ -6451,25 +6461,25 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B145" s="13">
-        <v>21.0</v>
+        <v>7.0</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E145" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F145" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G145" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H145" s="13" t="s">
         <v>17</v>
@@ -6494,14 +6504,30 @@
       <c r="Z145" s="9"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="5"/>
-      <c r="B146" s="8"/>
-      <c r="C146" s="8"/>
-      <c r="D146" s="11"/>
-      <c r="E146" s="8"/>
-      <c r="F146" s="8"/>
-      <c r="G146" s="8"/>
-      <c r="H146" s="8"/>
+      <c r="A146" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B146" s="13">
+        <v>21.0</v>
+      </c>
+      <c r="C146" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D146" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F146" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G146" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H146" s="13" t="s">
+        <v>17</v>
+      </c>
       <c r="I146" s="8"/>
       <c r="J146" s="8"/>
       <c r="K146" s="8"/>
@@ -6523,28 +6549,28 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B147" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D147" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E147" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F147" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G147" s="14" t="s">
+      <c r="B147" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="C147" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D147" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E147" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F147" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H147" s="8" t="s">
-        <v>69</v>
+      <c r="G147" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H147" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="I147" s="8"/>
       <c r="J147" s="8"/>
@@ -6567,28 +6593,28 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B148" s="8">
-        <v>6.0</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D148" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E148" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F148" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G148" s="14" t="s">
+      <c r="B148" s="13">
+        <v>21.0</v>
+      </c>
+      <c r="C148" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D148" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F148" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H148" s="8" t="s">
-        <v>69</v>
+      <c r="G148" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H148" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="I148" s="8"/>
       <c r="J148" s="8"/>
@@ -6613,7 +6639,7 @@
       <c r="A149" s="5"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
-      <c r="D149" s="11"/>
+      <c r="D149" s="10"/>
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
       <c r="G149" s="8"/>
@@ -6639,28 +6665,28 @@
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B150" s="8">
         <v>5.0</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F150" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G150" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="F150" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G150" s="14" t="s">
+        <v>84</v>
       </c>
       <c r="H150" s="8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I150" s="8"/>
       <c r="J150" s="8"/>
@@ -6683,28 +6709,28 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B151" s="8">
         <v>6.0</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F151" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G151" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="F151" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G151" s="14" t="s">
+        <v>84</v>
       </c>
       <c r="H151" s="8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I151" s="8"/>
       <c r="J151" s="8"/>
@@ -6729,7 +6755,7 @@
       <c r="A152" s="5"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
-      <c r="D152" s="11"/>
+      <c r="D152" s="10"/>
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
       <c r="G152" s="8"/>
@@ -6755,28 +6781,28 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B153" s="8">
         <v>5.0</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F153" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="G153" s="14" t="s">
-        <v>83</v>
+        <v>73</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="H153" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I153" s="8"/>
       <c r="J153" s="8"/>
@@ -6799,28 +6825,28 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B154" s="8">
         <v>6.0</v>
       </c>
       <c r="C154" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D154" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D154" s="8" t="s">
-        <v>87</v>
-      </c>
       <c r="E154" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F154" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="G154" s="14" t="s">
-        <v>83</v>
+        <v>73</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="H154" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I154" s="8"/>
       <c r="J154" s="8"/>
@@ -6845,7 +6871,7 @@
       <c r="A155" s="5"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
-      <c r="D155" s="11"/>
+      <c r="D155" s="10"/>
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
       <c r="G155" s="8"/>
@@ -6871,28 +6897,28 @@
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B156" s="8">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D156" s="11" t="s">
-        <v>86</v>
+        <v>91</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="F156" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G156" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H156" s="8" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="I156" s="8"/>
       <c r="J156" s="8"/>
@@ -6915,28 +6941,28 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B157" s="8">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D157" s="11" t="s">
-        <v>87</v>
+        <v>91</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="F157" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G157" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H157" s="8" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="I157" s="8"/>
       <c r="J157" s="8"/>
@@ -6961,7 +6987,7 @@
       <c r="A158" s="5"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
-      <c r="D158" s="11"/>
+      <c r="D158" s="10"/>
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
       <c r="G158" s="8"/>
@@ -6987,28 +7013,28 @@
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B159" s="8">
         <v>12.0</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D159" s="8" t="s">
-        <v>88</v>
+        <v>49</v>
+      </c>
+      <c r="D159" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="E159" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F159" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F159" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G159" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H159" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="G159" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H159" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="I159" s="8"/>
       <c r="J159" s="8"/>
@@ -7031,28 +7057,28 @@
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B160" s="8">
         <v>13.0</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D160" s="8" t="s">
-        <v>89</v>
+        <v>49</v>
+      </c>
+      <c r="D160" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="E160" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F160" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F160" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G160" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H160" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="G160" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H160" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="I160" s="8"/>
       <c r="J160" s="8"/>
@@ -7073,11 +7099,11 @@
       <c r="Y160" s="8"/>
       <c r="Z160" s="9"/>
     </row>
-    <row r="161" ht="15.0" customHeight="1">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="5"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
-      <c r="D161" s="11"/>
+      <c r="D161" s="10"/>
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
       <c r="G161" s="8"/>
@@ -7103,19 +7129,19 @@
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B162" s="8">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>28</v>
@@ -7124,7 +7150,7 @@
         <v>70</v>
       </c>
       <c r="H162" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I162" s="8"/>
       <c r="J162" s="8"/>
@@ -7147,19 +7173,19 @@
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B163" s="8">
-        <v>20.0</v>
+        <v>13.0</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>28</v>
@@ -7168,7 +7194,7 @@
         <v>70</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I163" s="8"/>
       <c r="J163" s="8"/>
@@ -7189,11 +7215,11 @@
       <c r="Y163" s="8"/>
       <c r="Z163" s="9"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="5"/>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
-      <c r="D164" s="11"/>
+      <c r="D164" s="10"/>
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
       <c r="G164" s="8"/>
@@ -7219,19 +7245,19 @@
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B165" s="8">
         <v>19.0</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E165" s="13" t="s">
-        <v>17</v>
+        <v>89</v>
+      </c>
+      <c r="E165" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>28</v>
@@ -7240,7 +7266,7 @@
         <v>70</v>
       </c>
       <c r="H165" s="8" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="I165" s="8"/>
       <c r="J165" s="8"/>
@@ -7263,28 +7289,28 @@
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B166" s="8">
         <v>20.0</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E166" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F166" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="G166" s="14" t="s">
-        <v>83</v>
+        <v>92</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="H166" s="8" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="I166" s="8"/>
       <c r="J166" s="8"/>
@@ -7306,30 +7332,14 @@
       <c r="Z166" s="9"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B167" s="8">
-        <v>19.0</v>
-      </c>
-      <c r="C167" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D167" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F167" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G167" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="H167" s="8" t="s">
-        <v>17</v>
-      </c>
+      <c r="A167" s="5"/>
+      <c r="B167" s="8"/>
+      <c r="C167" s="8"/>
+      <c r="D167" s="10"/>
+      <c r="E167" s="8"/>
+      <c r="F167" s="8"/>
+      <c r="G167" s="8"/>
+      <c r="H167" s="8"/>
       <c r="I167" s="8"/>
       <c r="J167" s="8"/>
       <c r="K167" s="8"/>
@@ -7351,25 +7361,25 @@
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B168" s="8">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E168" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E168" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F168" s="8" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H168" s="8" t="s">
         <v>17</v>
@@ -7394,14 +7404,30 @@
       <c r="Z168" s="9"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="5"/>
-      <c r="B169" s="8"/>
-      <c r="C169" s="8"/>
-      <c r="D169" s="11"/>
-      <c r="E169" s="8"/>
-      <c r="F169" s="8"/>
-      <c r="G169" s="8"/>
-      <c r="H169" s="8"/>
+      <c r="A169" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B169" s="8">
+        <v>20.0</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D169" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E169" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F169" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G169" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H169" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="I169" s="8"/>
       <c r="J169" s="8"/>
       <c r="K169" s="8"/>
@@ -7423,28 +7449,28 @@
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B170" s="8">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H170" s="8" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="I170" s="8"/>
       <c r="J170" s="8"/>
@@ -7467,28 +7493,28 @@
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B171" s="8">
-        <v>27.0</v>
+        <v>20.0</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="F171" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H171" s="8" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="I171" s="8"/>
       <c r="J171" s="8"/>
@@ -7513,7 +7539,7 @@
       <c r="A172" s="5"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
-      <c r="D172" s="11"/>
+      <c r="D172" s="10"/>
       <c r="E172" s="8"/>
       <c r="F172" s="8"/>
       <c r="G172" s="8"/>
@@ -7539,28 +7565,28 @@
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B173" s="8">
         <v>26.0</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="E173" s="8" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F173" s="8" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H173" s="8" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="I173" s="8"/>
       <c r="J173" s="8"/>
@@ -7583,28 +7609,28 @@
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B174" s="8">
         <v>27.0</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H174" s="8" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="I174" s="8"/>
       <c r="J174" s="8"/>
@@ -7626,30 +7652,14 @@
       <c r="Z174" s="9"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B175" s="8">
-        <v>26.0</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D175" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E175" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F175" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G175" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="H175" s="8" t="s">
-        <v>64</v>
-      </c>
+      <c r="A175" s="5"/>
+      <c r="B175" s="8"/>
+      <c r="C175" s="8"/>
+      <c r="D175" s="10"/>
+      <c r="E175" s="8"/>
+      <c r="F175" s="8"/>
+      <c r="G175" s="8"/>
+      <c r="H175" s="8"/>
       <c r="I175" s="8"/>
       <c r="J175" s="8"/>
       <c r="K175" s="8"/>
@@ -7671,25 +7681,25 @@
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B176" s="8">
-        <v>27.0</v>
+        <v>26.0</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="E176" s="8" t="s">
         <v>64</v>
       </c>
       <c r="F176" s="8" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H176" s="8" t="s">
         <v>64</v>
@@ -7714,14 +7724,30 @@
       <c r="Z176" s="9"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="5"/>
-      <c r="B177" s="8"/>
-      <c r="C177" s="8"/>
-      <c r="D177" s="11"/>
-      <c r="E177" s="8"/>
-      <c r="F177" s="8"/>
-      <c r="G177" s="8"/>
-      <c r="H177" s="8"/>
+      <c r="A177" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B177" s="8">
+        <v>27.0</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E177" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H177" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="I177" s="8"/>
       <c r="J177" s="8"/>
       <c r="K177" s="8"/>
@@ -7743,28 +7769,28 @@
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B178" s="8">
         <v>26.0</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F178" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H178" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I178" s="8"/>
       <c r="J178" s="8"/>
@@ -7787,28 +7813,28 @@
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B179" s="8">
         <v>27.0</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F179" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="G179" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F179" s="8" t="s">
         <v>83</v>
       </c>
+      <c r="G179" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="H179" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I179" s="8"/>
       <c r="J179" s="8"/>
@@ -7833,7 +7859,7 @@
       <c r="A180" s="5"/>
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
-      <c r="D180" s="11"/>
+      <c r="D180" s="10"/>
       <c r="E180" s="8"/>
       <c r="F180" s="8"/>
       <c r="G180" s="8"/>
@@ -7859,28 +7885,28 @@
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B181" s="15">
-        <v>27.0</v>
+        <v>82</v>
+      </c>
+      <c r="B181" s="8">
+        <v>26.0</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E181" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F181" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="G181" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F181" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="H181" s="6" t="s">
-        <v>53</v>
+      <c r="G181" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H181" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="I181" s="8"/>
       <c r="J181" s="8"/>
@@ -7903,28 +7929,28 @@
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B182" s="15">
-        <v>26.0</v>
+        <v>82</v>
+      </c>
+      <c r="B182" s="8">
+        <v>27.0</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E182" s="6" t="s">
-        <v>11</v>
+        <v>38</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="F182" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G182" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="H182" s="6" t="s">
-        <v>53</v>
+        <v>84</v>
+      </c>
+      <c r="H182" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="I182" s="8"/>
       <c r="J182" s="8"/>
@@ -7949,7 +7975,7 @@
       <c r="A183" s="5"/>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
-      <c r="D183" s="11"/>
+      <c r="D183" s="10"/>
       <c r="E183" s="8"/>
       <c r="F183" s="8"/>
       <c r="G183" s="8"/>
@@ -7975,28 +8001,28 @@
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B184" s="15">
+        <v>82</v>
+      </c>
+      <c r="B184" s="8">
         <v>27.0</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F184" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G184" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="H184" s="8" t="s">
-        <v>60</v>
+        <v>84</v>
+      </c>
+      <c r="H184" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="I184" s="8"/>
       <c r="J184" s="8"/>
@@ -8019,28 +8045,28 @@
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B185" s="15">
+        <v>82</v>
+      </c>
+      <c r="B185" s="8">
         <v>26.0</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E185" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F185" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G185" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="H185" s="8" t="s">
-        <v>60</v>
+        <v>84</v>
+      </c>
+      <c r="H185" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="I185" s="8"/>
       <c r="J185" s="8"/>
@@ -8062,57 +8088,57 @@
       <c r="Z185" s="9"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="16"/>
-      <c r="B186" s="13"/>
-      <c r="C186" s="13"/>
-      <c r="D186" s="17"/>
-      <c r="E186" s="13"/>
-      <c r="F186" s="13"/>
-      <c r="G186" s="13"/>
-      <c r="H186" s="13"/>
-      <c r="I186" s="13"/>
-      <c r="J186" s="13"/>
-      <c r="K186" s="13"/>
-      <c r="L186" s="13"/>
-      <c r="M186" s="13"/>
-      <c r="N186" s="13"/>
-      <c r="O186" s="13"/>
-      <c r="P186" s="13"/>
-      <c r="Q186" s="13"/>
-      <c r="R186" s="13"/>
-      <c r="S186" s="13"/>
-      <c r="T186" s="13"/>
-      <c r="U186" s="13"/>
-      <c r="V186" s="13"/>
-      <c r="W186" s="13"/>
-      <c r="X186" s="13"/>
-      <c r="Y186" s="13"/>
-      <c r="Z186" s="18"/>
+      <c r="A186" s="5"/>
+      <c r="B186" s="8"/>
+      <c r="C186" s="8"/>
+      <c r="D186" s="10"/>
+      <c r="E186" s="8"/>
+      <c r="F186" s="8"/>
+      <c r="G186" s="8"/>
+      <c r="H186" s="8"/>
+      <c r="I186" s="8"/>
+      <c r="J186" s="8"/>
+      <c r="K186" s="8"/>
+      <c r="L186" s="8"/>
+      <c r="M186" s="8"/>
+      <c r="N186" s="8"/>
+      <c r="O186" s="8"/>
+      <c r="P186" s="8"/>
+      <c r="Q186" s="8"/>
+      <c r="R186" s="8"/>
+      <c r="S186" s="8"/>
+      <c r="T186" s="8"/>
+      <c r="U186" s="8"/>
+      <c r="V186" s="8"/>
+      <c r="W186" s="8"/>
+      <c r="X186" s="8"/>
+      <c r="Y186" s="8"/>
+      <c r="Z186" s="9"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="5" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B187" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="C187" s="13" t="s">
-        <v>45</v>
+        <v>27.0</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E187" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F187" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G187" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H187" s="13" t="s">
-        <v>46</v>
+        <v>95</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F187" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G187" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H187" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="I187" s="8"/>
       <c r="J187" s="8"/>
@@ -8135,28 +8161,28 @@
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B188" s="8">
+        <v>26.0</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D188" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B188" s="8">
-        <v>19.0</v>
-      </c>
-      <c r="C188" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D188" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E188" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F188" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G188" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H188" s="13" t="s">
-        <v>46</v>
+      <c r="E188" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F188" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G188" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H188" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="I188" s="8"/>
       <c r="J188" s="8"/>
@@ -8178,61 +8204,57 @@
       <c r="Z188" s="9"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="5"/>
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
-      <c r="D189" s="11"/>
-      <c r="E189" s="8"/>
-      <c r="F189" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G189" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H189" s="8"/>
-      <c r="I189" s="8"/>
-      <c r="J189" s="8"/>
-      <c r="K189" s="8"/>
-      <c r="L189" s="8"/>
-      <c r="M189" s="8"/>
-      <c r="N189" s="8"/>
-      <c r="O189" s="8"/>
-      <c r="P189" s="8"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
-      <c r="S189" s="8"/>
-      <c r="T189" s="8"/>
-      <c r="U189" s="8"/>
-      <c r="V189" s="8"/>
-      <c r="W189" s="8"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="8"/>
-      <c r="Z189" s="9"/>
+      <c r="A189" s="15"/>
+      <c r="B189" s="13"/>
+      <c r="C189" s="13"/>
+      <c r="D189" s="16"/>
+      <c r="E189" s="13"/>
+      <c r="F189" s="13"/>
+      <c r="G189" s="13"/>
+      <c r="H189" s="13"/>
+      <c r="I189" s="13"/>
+      <c r="J189" s="13"/>
+      <c r="K189" s="13"/>
+      <c r="L189" s="13"/>
+      <c r="M189" s="13"/>
+      <c r="N189" s="13"/>
+      <c r="O189" s="13"/>
+      <c r="P189" s="13"/>
+      <c r="Q189" s="13"/>
+      <c r="R189" s="13"/>
+      <c r="S189" s="13"/>
+      <c r="T189" s="13"/>
+      <c r="U189" s="13"/>
+      <c r="V189" s="13"/>
+      <c r="W189" s="13"/>
+      <c r="X189" s="13"/>
+      <c r="Y189" s="13"/>
+      <c r="Z189" s="17"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="5" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="B190" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="C190" s="13" t="s">
-        <v>9</v>
+        <v>27.0</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>81</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E190" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F190" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G190" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H190" s="13" t="s">
-        <v>17</v>
+        <v>95</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F190" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G190" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H190" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="I190" s="8"/>
       <c r="J190" s="8"/>
@@ -8255,28 +8277,28 @@
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="5" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="B191" s="8">
-        <v>19.0</v>
-      </c>
-      <c r="C191" s="13" t="s">
-        <v>9</v>
+        <v>26.0</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>81</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E191" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F191" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G191" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H191" s="13" t="s">
-        <v>17</v>
+        <v>96</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F191" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G191" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H191" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="I191" s="8"/>
       <c r="J191" s="8"/>
@@ -8298,73 +8320,57 @@
       <c r="Z191" s="9"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B192" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="C192" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D192" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E192" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F192" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G192" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H192" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="I192" s="8"/>
-      <c r="J192" s="8"/>
-      <c r="K192" s="8"/>
-      <c r="L192" s="8"/>
-      <c r="M192" s="8"/>
-      <c r="N192" s="8"/>
-      <c r="O192" s="8"/>
-      <c r="P192" s="8"/>
-      <c r="Q192" s="8"/>
-      <c r="R192" s="8"/>
-      <c r="S192" s="8"/>
-      <c r="T192" s="8"/>
-      <c r="U192" s="8"/>
-      <c r="V192" s="8"/>
-      <c r="W192" s="8"/>
-      <c r="X192" s="8"/>
-      <c r="Y192" s="8"/>
-      <c r="Z192" s="9"/>
+      <c r="A192" s="18"/>
+      <c r="B192" s="13"/>
+      <c r="C192" s="13"/>
+      <c r="D192" s="16"/>
+      <c r="E192" s="13"/>
+      <c r="F192" s="13"/>
+      <c r="G192" s="13"/>
+      <c r="H192" s="13"/>
+      <c r="I192" s="13"/>
+      <c r="J192" s="13"/>
+      <c r="K192" s="13"/>
+      <c r="L192" s="13"/>
+      <c r="M192" s="13"/>
+      <c r="N192" s="13"/>
+      <c r="O192" s="13"/>
+      <c r="P192" s="13"/>
+      <c r="Q192" s="13"/>
+      <c r="R192" s="13"/>
+      <c r="S192" s="13"/>
+      <c r="T192" s="13"/>
+      <c r="U192" s="13"/>
+      <c r="V192" s="13"/>
+      <c r="W192" s="13"/>
+      <c r="X192" s="13"/>
+      <c r="Y192" s="13"/>
+      <c r="Z192" s="19"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B193" s="8">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
       <c r="C193" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D193" s="13" t="s">
-        <v>58</v>
+        <v>45</v>
+      </c>
+      <c r="D193" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="E193" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F193" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G193" s="13" t="s">
-        <v>101</v>
+        <v>46</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="H193" s="13" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="I193" s="8"/>
       <c r="J193" s="8"/>
@@ -8386,14 +8392,30 @@
       <c r="Z193" s="9"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="5"/>
-      <c r="B194" s="8"/>
-      <c r="C194" s="8"/>
-      <c r="D194" s="11"/>
-      <c r="E194" s="8"/>
-      <c r="F194" s="8"/>
-      <c r="G194" s="8"/>
-      <c r="H194" s="8"/>
+      <c r="A194" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B194" s="8">
+        <v>19.0</v>
+      </c>
+      <c r="C194" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D194" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E194" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H194" s="13" t="s">
+        <v>46</v>
+      </c>
       <c r="I194" s="8"/>
       <c r="J194" s="8"/>
       <c r="K194" s="8"/>
@@ -8414,30 +8436,18 @@
       <c r="Z194" s="9"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B195" s="8">
-        <v>10.0</v>
-      </c>
-      <c r="C195" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D195" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E195" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F195" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G195" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H195" s="8" t="s">
-        <v>69</v>
-      </c>
+      <c r="A195" s="5"/>
+      <c r="B195" s="8"/>
+      <c r="C195" s="8"/>
+      <c r="D195" s="10"/>
+      <c r="E195" s="8"/>
+      <c r="F195" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H195" s="8"/>
       <c r="I195" s="8"/>
       <c r="J195" s="8"/>
       <c r="K195" s="8"/>
@@ -8459,28 +8469,28 @@
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B196" s="8">
-        <v>11.0</v>
-      </c>
-      <c r="C196" s="8" t="s">
-        <v>71</v>
+        <v>5.0</v>
+      </c>
+      <c r="C196" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E196" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F196" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G196" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H196" s="8" t="s">
-        <v>69</v>
+        <v>89</v>
+      </c>
+      <c r="E196" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H196" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="I196" s="8"/>
       <c r="J196" s="8"/>
@@ -8502,14 +8512,30 @@
       <c r="Z196" s="9"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="5"/>
-      <c r="B197" s="8"/>
-      <c r="C197" s="8"/>
-      <c r="D197" s="11"/>
-      <c r="E197" s="8"/>
-      <c r="F197" s="8"/>
-      <c r="G197" s="8"/>
-      <c r="H197" s="8"/>
+      <c r="A197" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B197" s="8">
+        <v>19.0</v>
+      </c>
+      <c r="C197" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D197" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E197" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F197" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H197" s="13" t="s">
+        <v>17</v>
+      </c>
       <c r="I197" s="8"/>
       <c r="J197" s="8"/>
       <c r="K197" s="8"/>
@@ -8531,28 +8557,28 @@
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B198" s="8">
-        <v>10.0</v>
-      </c>
-      <c r="C198" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D198" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E198" s="8" t="s">
-        <v>73</v>
+        <v>5.0</v>
+      </c>
+      <c r="C198" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D198" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E198" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="F198" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G198" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H198" s="8" t="s">
-        <v>73</v>
+        <v>102</v>
+      </c>
+      <c r="H198" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="I198" s="8"/>
       <c r="J198" s="8"/>
@@ -8575,28 +8601,28 @@
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B199" s="8">
-        <v>11.0</v>
-      </c>
-      <c r="C199" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D199" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E199" s="8" t="s">
-        <v>73</v>
+        <v>19.0</v>
+      </c>
+      <c r="C199" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D199" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E199" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="F199" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G199" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H199" s="8" t="s">
-        <v>73</v>
+        <v>102</v>
+      </c>
+      <c r="H199" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="I199" s="8"/>
       <c r="J199" s="8"/>
@@ -8621,7 +8647,7 @@
       <c r="A200" s="5"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
-      <c r="D200" s="11"/>
+      <c r="D200" s="10"/>
       <c r="E200" s="8"/>
       <c r="F200" s="8"/>
       <c r="G200" s="8"/>
@@ -8647,28 +8673,28 @@
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B201" s="8">
         <v>10.0</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D201" s="11" t="s">
-        <v>88</v>
+        <v>71</v>
+      </c>
+      <c r="D201" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="E201" s="8" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F201" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G201" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H201" s="8" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I201" s="8"/>
       <c r="J201" s="8"/>
@@ -8691,28 +8717,28 @@
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B202" s="8">
         <v>11.0</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D202" s="11" t="s">
-        <v>97</v>
+        <v>71</v>
+      </c>
+      <c r="D202" s="8" t="s">
+        <v>104</v>
       </c>
       <c r="E202" s="8" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F202" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G202" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I202" s="8"/>
       <c r="J202" s="8"/>
@@ -8737,7 +8763,7 @@
       <c r="A203" s="5"/>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
-      <c r="D203" s="11"/>
+      <c r="D203" s="10"/>
       <c r="E203" s="8"/>
       <c r="F203" s="8"/>
       <c r="G203" s="8"/>
@@ -8763,28 +8789,28 @@
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B204" s="8">
         <v>10.0</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D204" s="11" t="s">
-        <v>88</v>
+        <v>74</v>
+      </c>
+      <c r="D204" s="8" t="s">
+        <v>105</v>
       </c>
       <c r="E204" s="8" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="F204" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G204" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H204" s="8" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="I204" s="8"/>
       <c r="J204" s="8"/>
@@ -8807,28 +8833,28 @@
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B205" s="8">
         <v>11.0</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D205" s="11" t="s">
-        <v>97</v>
+        <v>74</v>
+      </c>
+      <c r="D205" s="8" t="s">
+        <v>106</v>
       </c>
       <c r="E205" s="8" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="F205" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G205" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H205" s="8" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="I205" s="8"/>
       <c r="J205" s="8"/>
@@ -8853,7 +8879,7 @@
       <c r="A206" s="5"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
-      <c r="D206" s="11"/>
+      <c r="D206" s="10"/>
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
       <c r="G206" s="8"/>
@@ -8879,28 +8905,28 @@
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B207" s="8">
         <v>10.0</v>
       </c>
       <c r="C207" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D207" s="8" t="s">
-        <v>104</v>
+        <v>91</v>
+      </c>
+      <c r="D207" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="E207" s="8" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="F207" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G207" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H207" s="8" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="I207" s="8"/>
       <c r="J207" s="8"/>
@@ -8923,28 +8949,28 @@
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B208" s="8">
         <v>11.0</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D208" s="8" t="s">
-        <v>105</v>
+        <v>91</v>
+      </c>
+      <c r="D208" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="E208" s="8" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="F208" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G208" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H208" s="8" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="I208" s="8"/>
       <c r="J208" s="8"/>
@@ -8969,7 +8995,7 @@
       <c r="A209" s="5"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
-      <c r="D209" s="11"/>
+      <c r="D209" s="10"/>
       <c r="E209" s="8"/>
       <c r="F209" s="8"/>
       <c r="G209" s="8"/>
@@ -8995,28 +9021,28 @@
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B210" s="8">
-        <v>17.0</v>
+        <v>10.0</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D210" s="8" t="s">
-        <v>104</v>
+        <v>49</v>
+      </c>
+      <c r="D210" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="E210" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F210" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G210" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H210" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I210" s="8"/>
       <c r="J210" s="8"/>
@@ -9039,28 +9065,28 @@
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B211" s="8">
+        <v>11.0</v>
+      </c>
+      <c r="C211" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D211" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B211" s="8">
-        <v>18.0</v>
-      </c>
-      <c r="C211" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D211" s="8" t="s">
-        <v>105</v>
-      </c>
       <c r="E211" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F211" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G211" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H211" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I211" s="8"/>
       <c r="J211" s="8"/>
@@ -9085,7 +9111,7 @@
       <c r="A212" s="5"/>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
-      <c r="D212" s="11"/>
+      <c r="D212" s="10"/>
       <c r="E212" s="8"/>
       <c r="F212" s="8"/>
       <c r="G212" s="8"/>
@@ -9111,28 +9137,28 @@
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B213" s="8">
-        <v>17.0</v>
+        <v>10.0</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D213" s="11" t="s">
-        <v>88</v>
+        <v>43</v>
+      </c>
+      <c r="D213" s="8" t="s">
+        <v>105</v>
       </c>
       <c r="E213" s="8" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F213" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G213" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H213" s="8" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I213" s="8"/>
       <c r="J213" s="8"/>
@@ -9155,28 +9181,28 @@
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B214" s="8">
-        <v>18.0</v>
+        <v>11.0</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D214" s="11" t="s">
-        <v>97</v>
+        <v>43</v>
+      </c>
+      <c r="D214" s="8" t="s">
+        <v>106</v>
       </c>
       <c r="E214" s="8" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F214" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G214" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H214" s="8" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="I214" s="8"/>
       <c r="J214" s="8"/>
@@ -9201,7 +9227,7 @@
       <c r="A215" s="5"/>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
-      <c r="D215" s="11"/>
+      <c r="D215" s="10"/>
       <c r="E215" s="8"/>
       <c r="F215" s="8"/>
       <c r="G215" s="8"/>
@@ -9227,28 +9253,28 @@
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B216" s="8">
         <v>17.0</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D216" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E216" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F216" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G216" s="8" t="s">
-        <v>70</v>
+        <v>51</v>
+      </c>
+      <c r="F216" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G216" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="H216" s="8" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="I216" s="8"/>
       <c r="J216" s="8"/>
@@ -9271,28 +9297,28 @@
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B217" s="8">
         <v>18.0</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D217" s="8" t="s">
         <v>106</v>
       </c>
       <c r="E217" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F217" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G217" s="8" t="s">
-        <v>70</v>
+        <v>51</v>
+      </c>
+      <c r="F217" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G217" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="H217" s="8" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="I217" s="8"/>
       <c r="J217" s="8"/>
@@ -9317,7 +9343,7 @@
       <c r="A218" s="5"/>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
-      <c r="D218" s="11"/>
+      <c r="D218" s="10"/>
       <c r="E218" s="8"/>
       <c r="F218" s="8"/>
       <c r="G218" s="8"/>
@@ -9343,28 +9369,28 @@
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B219" s="8">
         <v>17.0</v>
       </c>
       <c r="C219" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D219" s="8" t="s">
-        <v>107</v>
+        <v>26</v>
+      </c>
+      <c r="D219" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="E219" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F219" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G219" s="8" t="s">
-        <v>70</v>
+        <v>17</v>
+      </c>
+      <c r="F219" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G219" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="H219" s="8" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="I219" s="8"/>
       <c r="J219" s="8"/>
@@ -9387,28 +9413,28 @@
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B220" s="8">
         <v>18.0</v>
       </c>
       <c r="C220" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D220" s="8" t="s">
-        <v>107</v>
+        <v>26</v>
+      </c>
+      <c r="D220" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="E220" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F220" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G220" s="8" t="s">
-        <v>70</v>
+        <v>17</v>
+      </c>
+      <c r="F220" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G220" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="H220" s="8" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="I220" s="8"/>
       <c r="J220" s="8"/>
@@ -9433,7 +9459,7 @@
       <c r="A221" s="5"/>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
-      <c r="D221" s="11"/>
+      <c r="D221" s="10"/>
       <c r="E221" s="8"/>
       <c r="F221" s="8"/>
       <c r="G221" s="8"/>
@@ -9459,28 +9485,28 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B222" s="8">
         <v>17.0</v>
       </c>
-      <c r="C222" s="13" t="s">
-        <v>66</v>
+      <c r="C222" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="D222" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E222" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F222" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G222" s="13" t="s">
-        <v>101</v>
+        <v>17</v>
+      </c>
+      <c r="F222" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G222" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="H222" s="8" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I222" s="8"/>
       <c r="J222" s="8"/>
@@ -9503,28 +9529,28 @@
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B223" s="8">
         <v>18.0</v>
       </c>
-      <c r="C223" s="13" t="s">
-        <v>66</v>
+      <c r="C223" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E223" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F223" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G223" s="13" t="s">
-        <v>101</v>
+        <v>17</v>
+      </c>
+      <c r="F223" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G223" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="H223" s="8" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I223" s="8"/>
       <c r="J223" s="8"/>
@@ -9546,30 +9572,14 @@
       <c r="Z223" s="9"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B224" s="8">
-        <v>17.0</v>
-      </c>
-      <c r="C224" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D224" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E224" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F224" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G224" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H224" s="13" t="s">
-        <v>64</v>
-      </c>
+      <c r="A224" s="5"/>
+      <c r="B224" s="8"/>
+      <c r="C224" s="8"/>
+      <c r="D224" s="10"/>
+      <c r="E224" s="8"/>
+      <c r="F224" s="8"/>
+      <c r="G224" s="8"/>
+      <c r="H224" s="8"/>
       <c r="I224" s="8"/>
       <c r="J224" s="8"/>
       <c r="K224" s="8"/>
@@ -9591,28 +9601,28 @@
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B225" s="8">
-        <v>18.0</v>
-      </c>
-      <c r="C225" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D225" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E225" s="13" t="s">
-        <v>64</v>
+        <v>17.0</v>
+      </c>
+      <c r="C225" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D225" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E225" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="F225" s="8" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H225" s="13" t="s">
-        <v>64</v>
+      <c r="H225" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="I225" s="8"/>
       <c r="J225" s="8"/>
@@ -9634,14 +9644,30 @@
       <c r="Z225" s="9"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="5"/>
-      <c r="B226" s="8"/>
-      <c r="C226" s="8"/>
-      <c r="D226" s="11"/>
-      <c r="E226" s="8"/>
-      <c r="F226" s="8"/>
-      <c r="G226" s="8"/>
-      <c r="H226" s="8"/>
+      <c r="A226" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B226" s="8">
+        <v>18.0</v>
+      </c>
+      <c r="C226" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D226" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E226" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F226" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G226" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H226" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="I226" s="8"/>
       <c r="J226" s="8"/>
       <c r="K226" s="8"/>
@@ -9662,30 +9688,14 @@
       <c r="Z226" s="9"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B227" s="8">
-        <v>17.0</v>
-      </c>
-      <c r="C227" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D227" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E227" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F227" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G227" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H227" s="13" t="s">
-        <v>60</v>
-      </c>
+      <c r="A227" s="5"/>
+      <c r="B227" s="8"/>
+      <c r="C227" s="8"/>
+      <c r="D227" s="10"/>
+      <c r="E227" s="8"/>
+      <c r="F227" s="8"/>
+      <c r="G227" s="8"/>
+      <c r="H227" s="8"/>
       <c r="I227" s="8"/>
       <c r="J227" s="8"/>
       <c r="K227" s="8"/>
@@ -9707,28 +9717,28 @@
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B228" s="8">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="C228" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D228" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E228" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F228" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G228" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H228" s="13" t="s">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="D228" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E228" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F228" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G228" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H228" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="I228" s="8"/>
       <c r="J228" s="8"/>
@@ -9750,14 +9760,30 @@
       <c r="Z228" s="9"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="5"/>
-      <c r="B229" s="8"/>
-      <c r="C229" s="8"/>
-      <c r="D229" s="11"/>
-      <c r="E229" s="8"/>
-      <c r="F229" s="8"/>
-      <c r="G229" s="8"/>
-      <c r="H229" s="8"/>
+      <c r="A229" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B229" s="8">
+        <v>18.0</v>
+      </c>
+      <c r="C229" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D229" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E229" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F229" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G229" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H229" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="I229" s="8"/>
       <c r="J229" s="8"/>
       <c r="K229" s="8"/>
@@ -9779,28 +9805,28 @@
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B230" s="8">
-        <v>31.0</v>
-      </c>
-      <c r="C230" s="8" t="s">
-        <v>80</v>
+        <v>17.0</v>
+      </c>
+      <c r="C230" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="D230" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E230" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F230" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G230" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H230" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="F230" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G230" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H230" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="I230" s="8"/>
       <c r="J230" s="8"/>
@@ -9823,28 +9849,28 @@
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B231" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="C231" s="8" t="s">
-        <v>80</v>
+        <v>18.0</v>
+      </c>
+      <c r="C231" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="D231" s="13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E231" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F231" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G231" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H231" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
+      </c>
+      <c r="F231" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G231" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H231" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="I231" s="8"/>
       <c r="J231" s="8"/>
@@ -9869,7 +9895,7 @@
       <c r="A232" s="5"/>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
-      <c r="D232" s="11"/>
+      <c r="D232" s="10"/>
       <c r="E232" s="8"/>
       <c r="F232" s="8"/>
       <c r="G232" s="8"/>
@@ -9895,28 +9921,28 @@
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B233" s="8">
-        <v>31.0</v>
-      </c>
-      <c r="C233" s="8" t="s">
-        <v>93</v>
+        <v>17.0</v>
+      </c>
+      <c r="C233" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="D233" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E233" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F233" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G233" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H233" s="8" t="s">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="F233" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G233" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H233" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="I233" s="8"/>
       <c r="J233" s="8"/>
@@ -9939,28 +9965,28 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B234" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="C234" s="8" t="s">
-        <v>77</v>
+        <v>18.0</v>
+      </c>
+      <c r="C234" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="D234" s="13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E234" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F234" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G234" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H234" s="8" t="s">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="F234" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G234" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H234" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="I234" s="8"/>
       <c r="J234" s="8"/>
@@ -9982,57 +10008,57 @@
       <c r="Z234" s="9"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="16"/>
-      <c r="B235" s="13"/>
-      <c r="C235" s="13"/>
-      <c r="D235" s="17"/>
-      <c r="E235" s="13"/>
-      <c r="F235" s="13"/>
-      <c r="G235" s="13"/>
-      <c r="H235" s="13"/>
-      <c r="I235" s="13"/>
-      <c r="J235" s="13"/>
-      <c r="K235" s="13"/>
-      <c r="L235" s="13"/>
-      <c r="M235" s="13"/>
-      <c r="N235" s="13"/>
-      <c r="O235" s="13"/>
-      <c r="P235" s="13"/>
-      <c r="Q235" s="13"/>
-      <c r="R235" s="13"/>
-      <c r="S235" s="13"/>
-      <c r="T235" s="13"/>
-      <c r="U235" s="13"/>
-      <c r="V235" s="13"/>
-      <c r="W235" s="13"/>
-      <c r="X235" s="13"/>
-      <c r="Y235" s="13"/>
-      <c r="Z235" s="18"/>
+      <c r="A235" s="5"/>
+      <c r="B235" s="8"/>
+      <c r="C235" s="8"/>
+      <c r="D235" s="10"/>
+      <c r="E235" s="8"/>
+      <c r="F235" s="8"/>
+      <c r="G235" s="8"/>
+      <c r="H235" s="8"/>
+      <c r="I235" s="8"/>
+      <c r="J235" s="8"/>
+      <c r="K235" s="8"/>
+      <c r="L235" s="8"/>
+      <c r="M235" s="8"/>
+      <c r="N235" s="8"/>
+      <c r="O235" s="8"/>
+      <c r="P235" s="8"/>
+      <c r="Q235" s="8"/>
+      <c r="R235" s="8"/>
+      <c r="S235" s="8"/>
+      <c r="T235" s="8"/>
+      <c r="U235" s="8"/>
+      <c r="V235" s="8"/>
+      <c r="W235" s="8"/>
+      <c r="X235" s="8"/>
+      <c r="Y235" s="8"/>
+      <c r="Z235" s="9"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B236" s="8">
+        <v>31.0</v>
+      </c>
+      <c r="C236" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D236" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B236" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="C236" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D236" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E236" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F236" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G236" s="8" t="s">
-        <v>113</v>
+      <c r="E236" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F236" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G236" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="H236" s="8" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I236" s="8"/>
       <c r="J236" s="8"/>
@@ -10055,28 +10081,28 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B237" s="8">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="C237" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D237" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E237" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F237" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G237" s="8" t="s">
-        <v>113</v>
+        <v>80</v>
+      </c>
+      <c r="D237" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E237" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F237" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G237" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="H237" s="8" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I237" s="8"/>
       <c r="J237" s="8"/>
@@ -10101,7 +10127,7 @@
       <c r="A238" s="5"/>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
-      <c r="D238" s="11"/>
+      <c r="D238" s="10"/>
       <c r="E238" s="8"/>
       <c r="F238" s="8"/>
       <c r="G238" s="8"/>
@@ -10127,28 +10153,28 @@
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B239" s="8">
+        <v>31.0</v>
+      </c>
+      <c r="C239" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D239" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B239" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="C239" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D239" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E239" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F239" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G239" s="8" t="s">
-        <v>113</v>
+      <c r="E239" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F239" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G239" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="H239" s="8" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I239" s="8"/>
       <c r="J239" s="8"/>
@@ -10171,28 +10197,28 @@
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B240" s="8">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="C240" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D240" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E240" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F240" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G240" s="8" t="s">
-        <v>113</v>
+        <v>77</v>
+      </c>
+      <c r="D240" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E240" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F240" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G240" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="H240" s="8" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I240" s="8"/>
       <c r="J240" s="8"/>
@@ -10214,73 +10240,57 @@
       <c r="Z240" s="9"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B241" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="C241" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D241" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E241" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F241" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G241" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H241" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I241" s="8"/>
-      <c r="J241" s="8"/>
-      <c r="K241" s="8"/>
-      <c r="L241" s="8"/>
-      <c r="M241" s="8"/>
-      <c r="N241" s="8"/>
-      <c r="O241" s="8"/>
-      <c r="P241" s="8"/>
-      <c r="Q241" s="8"/>
-      <c r="R241" s="8"/>
-      <c r="S241" s="8"/>
-      <c r="T241" s="8"/>
-      <c r="U241" s="8"/>
-      <c r="V241" s="8"/>
-      <c r="W241" s="8"/>
-      <c r="X241" s="8"/>
-      <c r="Y241" s="8"/>
-      <c r="Z241" s="9"/>
+      <c r="A241" s="15"/>
+      <c r="B241" s="13"/>
+      <c r="C241" s="13"/>
+      <c r="D241" s="16"/>
+      <c r="E241" s="13"/>
+      <c r="F241" s="13"/>
+      <c r="G241" s="13"/>
+      <c r="H241" s="13"/>
+      <c r="I241" s="13"/>
+      <c r="J241" s="13"/>
+      <c r="K241" s="13"/>
+      <c r="L241" s="13"/>
+      <c r="M241" s="13"/>
+      <c r="N241" s="13"/>
+      <c r="O241" s="13"/>
+      <c r="P241" s="13"/>
+      <c r="Q241" s="13"/>
+      <c r="R241" s="13"/>
+      <c r="S241" s="13"/>
+      <c r="T241" s="13"/>
+      <c r="U241" s="13"/>
+      <c r="V241" s="13"/>
+      <c r="W241" s="13"/>
+      <c r="X241" s="13"/>
+      <c r="Y241" s="13"/>
+      <c r="Z241" s="17"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B242" s="8">
+        <v>31.0</v>
+      </c>
+      <c r="C242" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D242" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B242" s="8">
-        <v>16.0</v>
-      </c>
-      <c r="C242" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D242" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E242" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F242" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G242" s="8" t="s">
-        <v>70</v>
+      <c r="E242" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F242" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G242" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="H242" s="8" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I242" s="8"/>
       <c r="J242" s="8"/>
@@ -10302,14 +10312,30 @@
       <c r="Z242" s="9"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="5"/>
-      <c r="B243" s="8"/>
-      <c r="C243" s="8"/>
-      <c r="D243" s="11"/>
-      <c r="E243" s="8"/>
-      <c r="F243" s="8"/>
-      <c r="G243" s="8"/>
-      <c r="H243" s="8"/>
+      <c r="A243" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B243" s="8">
+        <v>1.0</v>
+      </c>
+      <c r="C243" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D243" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E243" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F243" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G243" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H243" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="I243" s="8"/>
       <c r="J243" s="8"/>
       <c r="K243" s="8"/>
@@ -10330,73 +10356,57 @@
       <c r="Z243" s="9"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B244" s="8">
-        <v>7.0</v>
-      </c>
-      <c r="C244" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D244" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E244" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F244" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G244" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="H244" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I244" s="8"/>
-      <c r="J244" s="8"/>
-      <c r="K244" s="8"/>
-      <c r="L244" s="8"/>
-      <c r="M244" s="8"/>
-      <c r="N244" s="8"/>
-      <c r="O244" s="8"/>
-      <c r="P244" s="8"/>
-      <c r="Q244" s="8"/>
-      <c r="R244" s="8"/>
-      <c r="S244" s="8"/>
-      <c r="T244" s="8"/>
-      <c r="U244" s="8"/>
-      <c r="V244" s="8"/>
-      <c r="W244" s="8"/>
-      <c r="X244" s="8"/>
-      <c r="Y244" s="8"/>
-      <c r="Z244" s="9"/>
+      <c r="A244" s="18"/>
+      <c r="B244" s="13"/>
+      <c r="C244" s="13"/>
+      <c r="D244" s="16"/>
+      <c r="E244" s="13"/>
+      <c r="F244" s="13"/>
+      <c r="G244" s="13"/>
+      <c r="H244" s="13"/>
+      <c r="I244" s="13"/>
+      <c r="J244" s="13"/>
+      <c r="K244" s="13"/>
+      <c r="L244" s="13"/>
+      <c r="M244" s="13"/>
+      <c r="N244" s="13"/>
+      <c r="O244" s="13"/>
+      <c r="P244" s="13"/>
+      <c r="Q244" s="13"/>
+      <c r="R244" s="13"/>
+      <c r="S244" s="13"/>
+      <c r="T244" s="13"/>
+      <c r="U244" s="13"/>
+      <c r="V244" s="13"/>
+      <c r="W244" s="13"/>
+      <c r="X244" s="13"/>
+      <c r="Y244" s="13"/>
+      <c r="Z244" s="19"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B245" s="8">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="C245" s="8" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E245" s="8" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="F245" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G245" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H245" s="8" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I245" s="8"/>
       <c r="J245" s="8"/>
@@ -10418,14 +10428,30 @@
       <c r="Z245" s="9"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="5"/>
-      <c r="B246" s="8"/>
-      <c r="C246" s="8"/>
-      <c r="D246" s="11"/>
-      <c r="E246" s="8"/>
-      <c r="F246" s="8"/>
-      <c r="G246" s="8"/>
-      <c r="H246" s="8"/>
+      <c r="A246" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B246" s="8">
+        <v>16.0</v>
+      </c>
+      <c r="C246" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D246" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E246" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F246" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G246" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H246" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="I246" s="8"/>
       <c r="J246" s="8"/>
       <c r="K246" s="8"/>
@@ -10446,30 +10472,14 @@
       <c r="Z246" s="9"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B247" s="8">
-        <v>7.0</v>
-      </c>
-      <c r="C247" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D247" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E247" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F247" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G247" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="H247" s="8" t="s">
-        <v>73</v>
-      </c>
+      <c r="A247" s="5"/>
+      <c r="B247" s="8"/>
+      <c r="C247" s="8"/>
+      <c r="D247" s="10"/>
+      <c r="E247" s="8"/>
+      <c r="F247" s="8"/>
+      <c r="G247" s="8"/>
+      <c r="H247" s="8"/>
       <c r="I247" s="8"/>
       <c r="J247" s="8"/>
       <c r="K247" s="8"/>
@@ -10490,30 +10500,14 @@
       <c r="Z247" s="9"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B248" s="8">
-        <v>8.0</v>
-      </c>
-      <c r="C248" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D248" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E248" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F248" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G248" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="H248" s="8" t="s">
-        <v>73</v>
-      </c>
+      <c r="A248" s="5"/>
+      <c r="B248" s="8"/>
+      <c r="C248" s="8"/>
+      <c r="D248" s="10"/>
+      <c r="E248" s="8"/>
+      <c r="F248" s="8"/>
+      <c r="G248" s="8"/>
+      <c r="H248" s="8"/>
       <c r="I248" s="8"/>
       <c r="J248" s="8"/>
       <c r="K248" s="8"/>
@@ -10537,7 +10531,7 @@
       <c r="A249" s="5"/>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
-      <c r="D249" s="11"/>
+      <c r="D249" s="10"/>
       <c r="E249" s="8"/>
       <c r="F249" s="8"/>
       <c r="G249" s="8"/>
@@ -10562,30 +10556,14 @@
       <c r="Z249" s="9"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B250" s="8">
-        <v>7.0</v>
-      </c>
-      <c r="C250" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D250" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E250" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F250" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G250" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="H250" s="8" t="s">
-        <v>76</v>
-      </c>
+      <c r="A250" s="5"/>
+      <c r="B250" s="8"/>
+      <c r="C250" s="8"/>
+      <c r="D250" s="10"/>
+      <c r="E250" s="8"/>
+      <c r="F250" s="8"/>
+      <c r="G250" s="8"/>
+      <c r="H250" s="8"/>
       <c r="I250" s="8"/>
       <c r="J250" s="8"/>
       <c r="K250" s="8"/>
@@ -10607,28 +10585,28 @@
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B251" s="8">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="C251" s="8" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E251" s="8" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="F251" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G251" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H251" s="8" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="I251" s="8"/>
       <c r="J251" s="8"/>
@@ -10650,14 +10628,30 @@
       <c r="Z251" s="9"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="5"/>
-      <c r="B252" s="8"/>
-      <c r="C252" s="8"/>
-      <c r="D252" s="11"/>
-      <c r="E252" s="8"/>
-      <c r="F252" s="8"/>
-      <c r="G252" s="8"/>
-      <c r="H252" s="8"/>
+      <c r="A252" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B252" s="8">
+        <v>16.0</v>
+      </c>
+      <c r="C252" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D252" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E252" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F252" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H252" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="I252" s="8"/>
       <c r="J252" s="8"/>
       <c r="K252" s="8"/>
@@ -10679,28 +10673,28 @@
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B253" s="8">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="C253" s="8" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="D253" s="8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E253" s="8" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F253" s="8" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="G253" s="8" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="H253" s="8" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I253" s="8"/>
       <c r="J253" s="8"/>
@@ -10723,28 +10717,28 @@
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B254" s="8">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="C254" s="8" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E254" s="8" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F254" s="8" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="G254" s="8" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="H254" s="8" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I254" s="8"/>
       <c r="J254" s="8"/>
@@ -10769,7 +10763,7 @@
       <c r="A255" s="5"/>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
-      <c r="D255" s="11"/>
+      <c r="D255" s="10"/>
       <c r="E255" s="8"/>
       <c r="F255" s="8"/>
       <c r="G255" s="8"/>
@@ -10795,28 +10789,28 @@
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B256" s="8">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="C256" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="E256" s="8" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="F256" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G256" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H256" s="8" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="I256" s="8"/>
       <c r="J256" s="8"/>
@@ -10839,28 +10833,28 @@
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B257" s="8">
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="C257" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E257" s="8" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="F257" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G257" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H257" s="8" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="I257" s="8"/>
       <c r="J257" s="8"/>
@@ -10885,7 +10879,7 @@
       <c r="A258" s="5"/>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
-      <c r="D258" s="11"/>
+      <c r="D258" s="10"/>
       <c r="E258" s="8"/>
       <c r="F258" s="8"/>
       <c r="G258" s="8"/>
@@ -10911,28 +10905,28 @@
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B259" s="8">
-        <v>21.0</v>
+        <v>7.0</v>
       </c>
       <c r="C259" s="8" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E259" s="8" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="F259" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G259" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H259" s="8" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="I259" s="8"/>
       <c r="J259" s="8"/>
@@ -10955,28 +10949,28 @@
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B260" s="8">
-        <v>22.0</v>
+        <v>8.0</v>
       </c>
       <c r="C260" s="8" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D260" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E260" s="8" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="F260" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G260" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H260" s="8" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="I260" s="8"/>
       <c r="J260" s="8"/>
@@ -11001,7 +10995,7 @@
       <c r="A261" s="5"/>
       <c r="B261" s="8"/>
       <c r="C261" s="8"/>
-      <c r="D261" s="11"/>
+      <c r="D261" s="10"/>
       <c r="E261" s="8"/>
       <c r="F261" s="8"/>
       <c r="G261" s="8"/>
@@ -11027,28 +11021,28 @@
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B262" s="8">
-        <v>21.0</v>
+        <v>7.0</v>
       </c>
       <c r="C262" s="8" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="D262" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E262" s="8" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="F262" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G262" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H262" s="8" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="I262" s="8"/>
       <c r="J262" s="8"/>
@@ -11071,28 +11065,28 @@
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B263" s="8">
-        <v>22.0</v>
+        <v>8.0</v>
       </c>
       <c r="C263" s="8" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E263" s="8" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="F263" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G263" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H263" s="8" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="I263" s="8"/>
       <c r="J263" s="8"/>
@@ -11117,7 +11111,7 @@
       <c r="A264" s="5"/>
       <c r="B264" s="8"/>
       <c r="C264" s="8"/>
-      <c r="D264" s="11"/>
+      <c r="D264" s="10"/>
       <c r="E264" s="8"/>
       <c r="F264" s="8"/>
       <c r="G264" s="8"/>
@@ -11143,28 +11137,28 @@
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B265" s="8">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="C265" s="8" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E265" s="8" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F265" s="8" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="G265" s="8" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="H265" s="8" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="I265" s="8"/>
       <c r="J265" s="8"/>
@@ -11187,28 +11181,28 @@
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B266" s="8">
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
       <c r="C266" s="8" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E266" s="8" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F266" s="8" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="G266" s="8" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="H266" s="8" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="I266" s="8"/>
       <c r="J266" s="8"/>
@@ -11233,7 +11227,7 @@
       <c r="A267" s="5"/>
       <c r="B267" s="8"/>
       <c r="C267" s="8"/>
-      <c r="D267" s="11"/>
+      <c r="D267" s="10"/>
       <c r="E267" s="8"/>
       <c r="F267" s="8"/>
       <c r="G267" s="8"/>
@@ -11259,28 +11253,28 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B268" s="8">
-        <v>28.0</v>
+        <v>14.0</v>
       </c>
       <c r="C268" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D268" s="14" t="s">
-        <v>106</v>
+        <v>43</v>
+      </c>
+      <c r="D268" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="E268" s="8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F268" s="8" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="G268" s="8" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="H268" s="8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="I268" s="8"/>
       <c r="J268" s="8"/>
@@ -11303,28 +11297,28 @@
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B269" s="8">
-        <v>29.0</v>
+        <v>15.0</v>
       </c>
       <c r="C269" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D269" s="14" t="s">
-        <v>106</v>
+        <v>43</v>
+      </c>
+      <c r="D269" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="E269" s="8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F269" s="8" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="G269" s="8" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="H269" s="8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="I269" s="8"/>
       <c r="J269" s="8"/>
@@ -11349,7 +11343,7 @@
       <c r="A270" s="5"/>
       <c r="B270" s="8"/>
       <c r="C270" s="8"/>
-      <c r="D270" s="11"/>
+      <c r="D270" s="10"/>
       <c r="E270" s="8"/>
       <c r="F270" s="8"/>
       <c r="G270" s="8"/>
@@ -11375,28 +11369,28 @@
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B271" s="8">
-        <v>28.0</v>
+        <v>21.0</v>
       </c>
       <c r="C271" s="8" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D271" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E271" s="8" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F271" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G271" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H271" s="8" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="I271" s="8"/>
       <c r="J271" s="8"/>
@@ -11419,28 +11413,28 @@
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B272" s="8">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
       <c r="C272" s="8" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D272" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E272" s="8" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F272" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G272" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H272" s="8" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="I272" s="8"/>
       <c r="J272" s="8"/>
@@ -11462,30 +11456,14 @@
       <c r="Z272" s="9"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="A273" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B273" s="8">
-        <v>28.0</v>
-      </c>
-      <c r="C273" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D273" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E273" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F273" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G273" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H273" s="8" t="s">
-        <v>64</v>
-      </c>
+      <c r="A273" s="5"/>
+      <c r="B273" s="8"/>
+      <c r="C273" s="8"/>
+      <c r="D273" s="10"/>
+      <c r="E273" s="8"/>
+      <c r="F273" s="8"/>
+      <c r="G273" s="8"/>
+      <c r="H273" s="8"/>
       <c r="I273" s="8"/>
       <c r="J273" s="8"/>
       <c r="K273" s="8"/>
@@ -11507,28 +11485,28 @@
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B274" s="8">
-        <v>29.0</v>
+        <v>21.0</v>
       </c>
       <c r="C274" s="8" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="D274" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E274" s="8" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="F274" s="8" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="G274" s="8" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="H274" s="8" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="I274" s="8"/>
       <c r="J274" s="8"/>
@@ -11550,14 +11528,30 @@
       <c r="Z274" s="9"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="5"/>
-      <c r="B275" s="8"/>
-      <c r="C275" s="8"/>
-      <c r="D275" s="8"/>
-      <c r="E275" s="8"/>
-      <c r="F275" s="8"/>
-      <c r="G275" s="8"/>
-      <c r="H275" s="8"/>
+      <c r="A275" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B275" s="8">
+        <v>22.0</v>
+      </c>
+      <c r="C275" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D275" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E275" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F275" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G275" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H275" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="I275" s="8"/>
       <c r="J275" s="8"/>
       <c r="K275" s="8"/>
@@ -11578,30 +11572,14 @@
       <c r="Z275" s="9"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B276" s="8">
-        <v>28.0</v>
-      </c>
-      <c r="C276" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D276" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E276" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F276" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G276" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H276" s="8" t="s">
-        <v>60</v>
-      </c>
+      <c r="A276" s="5"/>
+      <c r="B276" s="8"/>
+      <c r="C276" s="8"/>
+      <c r="D276" s="10"/>
+      <c r="E276" s="8"/>
+      <c r="F276" s="8"/>
+      <c r="G276" s="8"/>
+      <c r="H276" s="8"/>
       <c r="I276" s="8"/>
       <c r="J276" s="8"/>
       <c r="K276" s="8"/>
@@ -11623,19 +11601,19 @@
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B277" s="8">
-        <v>29.0</v>
+        <v>21.0</v>
       </c>
       <c r="C277" s="8" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D277" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E277" s="8" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="F277" s="8" t="s">
         <v>42</v>
@@ -11644,7 +11622,7 @@
         <v>70</v>
       </c>
       <c r="H277" s="8" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="I277" s="8"/>
       <c r="J277" s="8"/>
@@ -11666,14 +11644,30 @@
       <c r="Z277" s="9"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="5"/>
-      <c r="B278" s="8"/>
-      <c r="C278" s="8"/>
-      <c r="D278" s="8"/>
-      <c r="E278" s="8"/>
-      <c r="F278" s="8"/>
-      <c r="G278" s="8"/>
-      <c r="H278" s="8"/>
+      <c r="A278" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B278" s="8">
+        <v>22.0</v>
+      </c>
+      <c r="C278" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D278" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E278" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F278" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G278" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H278" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="I278" s="8"/>
       <c r="J278" s="8"/>
       <c r="K278" s="8"/>
@@ -11694,30 +11688,14 @@
       <c r="Z278" s="9"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B279" s="8">
-        <v>28.0</v>
-      </c>
-      <c r="C279" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D279" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E279" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F279" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="G279" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="H279" s="8" t="s">
-        <v>60</v>
-      </c>
+      <c r="A279" s="5"/>
+      <c r="B279" s="8"/>
+      <c r="C279" s="8"/>
+      <c r="D279" s="10"/>
+      <c r="E279" s="8"/>
+      <c r="F279" s="8"/>
+      <c r="G279" s="8"/>
+      <c r="H279" s="8"/>
       <c r="I279" s="8"/>
       <c r="J279" s="8"/>
       <c r="K279" s="8"/>
@@ -11739,28 +11717,28 @@
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B280" s="8">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="C280" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D280" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E280" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F280" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="G280" s="13" t="s">
-        <v>113</v>
+        <v>54</v>
+      </c>
+      <c r="D280" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E280" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F280" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G280" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="H280" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I280" s="8"/>
       <c r="J280" s="8"/>
@@ -11782,14 +11760,30 @@
       <c r="Z280" s="9"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="5"/>
-      <c r="B281" s="8"/>
-      <c r="C281" s="8"/>
-      <c r="D281" s="8"/>
-      <c r="E281" s="8"/>
-      <c r="F281" s="8"/>
-      <c r="G281" s="8"/>
-      <c r="H281" s="8"/>
+      <c r="A281" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B281" s="8">
+        <v>29.0</v>
+      </c>
+      <c r="C281" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D281" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E281" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F281" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G281" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H281" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="I281" s="8"/>
       <c r="J281" s="8"/>
       <c r="K281" s="8"/>
@@ -11810,30 +11804,14 @@
       <c r="Z281" s="9"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B282" s="8">
-        <v>28.0</v>
-      </c>
-      <c r="C282" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D282" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E282" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F282" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="G282" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="H282" s="8" t="s">
-        <v>53</v>
-      </c>
+      <c r="A282" s="5"/>
+      <c r="B282" s="8"/>
+      <c r="C282" s="8"/>
+      <c r="D282" s="10"/>
+      <c r="E282" s="8"/>
+      <c r="F282" s="8"/>
+      <c r="G282" s="8"/>
+      <c r="H282" s="8"/>
       <c r="I282" s="8"/>
       <c r="J282" s="8"/>
       <c r="K282" s="8"/>
@@ -11855,28 +11833,28 @@
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B283" s="8">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D283" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E283" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F283" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="G283" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D283" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E283" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F283" s="8" t="s">
         <v>113</v>
       </c>
+      <c r="G283" s="8" t="s">
+        <v>114</v>
+      </c>
       <c r="H283" s="8" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="I283" s="8"/>
       <c r="J283" s="8"/>
@@ -11898,42 +11876,74 @@
       <c r="Z283" s="9"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="A284" s="16"/>
-      <c r="B284" s="13"/>
-      <c r="C284" s="13"/>
-      <c r="D284" s="13"/>
-      <c r="E284" s="13"/>
-      <c r="F284" s="13"/>
-      <c r="G284" s="13"/>
-      <c r="H284" s="13"/>
-      <c r="I284" s="13"/>
-      <c r="J284" s="13"/>
-      <c r="K284" s="13"/>
-      <c r="L284" s="13"/>
-      <c r="M284" s="13"/>
-      <c r="N284" s="13"/>
-      <c r="O284" s="13"/>
-      <c r="P284" s="13"/>
-      <c r="Q284" s="13"/>
-      <c r="R284" s="13"/>
-      <c r="S284" s="13"/>
-      <c r="T284" s="13"/>
-      <c r="U284" s="13"/>
-      <c r="V284" s="13"/>
-      <c r="W284" s="13"/>
-      <c r="X284" s="13"/>
-      <c r="Y284" s="13"/>
-      <c r="Z284" s="18"/>
+      <c r="A284" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B284" s="8">
+        <v>29.0</v>
+      </c>
+      <c r="C284" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D284" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E284" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F284" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G284" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H284" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I284" s="8"/>
+      <c r="J284" s="8"/>
+      <c r="K284" s="8"/>
+      <c r="L284" s="8"/>
+      <c r="M284" s="8"/>
+      <c r="N284" s="8"/>
+      <c r="O284" s="8"/>
+      <c r="P284" s="8"/>
+      <c r="Q284" s="8"/>
+      <c r="R284" s="8"/>
+      <c r="S284" s="8"/>
+      <c r="T284" s="8"/>
+      <c r="U284" s="8"/>
+      <c r="V284" s="8"/>
+      <c r="W284" s="8"/>
+      <c r="X284" s="8"/>
+      <c r="Y284" s="8"/>
+      <c r="Z284" s="9"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="5"/>
-      <c r="B285" s="8"/>
-      <c r="C285" s="8"/>
-      <c r="D285" s="8"/>
-      <c r="E285" s="8"/>
-      <c r="F285" s="8"/>
-      <c r="G285" s="8"/>
-      <c r="H285" s="8"/>
+      <c r="A285" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B285" s="8">
+        <v>28.0</v>
+      </c>
+      <c r="C285" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D285" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E285" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F285" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G285" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H285" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="I285" s="8"/>
       <c r="J285" s="8"/>
       <c r="K285" s="8"/>
@@ -11955,28 +11965,28 @@
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B286" s="13">
-        <v>7.0</v>
-      </c>
-      <c r="C286" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D286" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E286" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F286" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G286" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H286" s="13" t="s">
-        <v>46</v>
+        <v>110</v>
+      </c>
+      <c r="B286" s="8">
+        <v>29.0</v>
+      </c>
+      <c r="C286" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D286" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E286" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F286" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G286" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H286" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="I286" s="8"/>
       <c r="J286" s="8"/>
@@ -11998,30 +12008,14 @@
       <c r="Z286" s="9"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B287" s="13">
-        <v>14.0</v>
-      </c>
-      <c r="C287" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D287" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E287" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F287" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G287" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H287" s="13" t="s">
-        <v>46</v>
-      </c>
+      <c r="A287" s="5"/>
+      <c r="B287" s="8"/>
+      <c r="C287" s="8"/>
+      <c r="D287" s="8"/>
+      <c r="E287" s="8"/>
+      <c r="F287" s="8"/>
+      <c r="G287" s="8"/>
+      <c r="H287" s="8"/>
       <c r="I287" s="8"/>
       <c r="J287" s="8"/>
       <c r="K287" s="8"/>
@@ -12042,14 +12036,30 @@
       <c r="Z287" s="9"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="5"/>
-      <c r="B288" s="8"/>
-      <c r="C288" s="8"/>
-      <c r="D288" s="8"/>
-      <c r="E288" s="8"/>
-      <c r="F288" s="8"/>
-      <c r="G288" s="8"/>
-      <c r="H288" s="8"/>
+      <c r="A288" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B288" s="8">
+        <v>28.0</v>
+      </c>
+      <c r="C288" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D288" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E288" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F288" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G288" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H288" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="I288" s="8"/>
       <c r="J288" s="8"/>
       <c r="K288" s="8"/>
@@ -12071,28 +12081,28 @@
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B289" s="13">
-        <v>7.0</v>
-      </c>
-      <c r="C289" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D289" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E289" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F289" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G289" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H289" s="13" t="s">
-        <v>17</v>
+        <v>110</v>
+      </c>
+      <c r="B289" s="8">
+        <v>29.0</v>
+      </c>
+      <c r="C289" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D289" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E289" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F289" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G289" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H289" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="I289" s="8"/>
       <c r="J289" s="8"/>
@@ -12114,30 +12124,14 @@
       <c r="Z289" s="9"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="A290" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B290" s="13">
-        <v>14.0</v>
-      </c>
-      <c r="C290" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D290" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E290" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F290" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G290" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H290" s="13" t="s">
-        <v>17</v>
-      </c>
+      <c r="A290" s="5"/>
+      <c r="B290" s="8"/>
+      <c r="C290" s="8"/>
+      <c r="D290" s="8"/>
+      <c r="E290" s="8"/>
+      <c r="F290" s="8"/>
+      <c r="G290" s="8"/>
+      <c r="H290" s="8"/>
       <c r="I290" s="8"/>
       <c r="J290" s="8"/>
       <c r="K290" s="8"/>
@@ -12159,28 +12153,28 @@
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B291" s="13">
-        <v>7.0</v>
-      </c>
-      <c r="C291" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D291" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
+      </c>
+      <c r="B291" s="8">
+        <v>28.0</v>
+      </c>
+      <c r="C291" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D291" s="8" t="s">
+        <v>117</v>
       </c>
       <c r="E291" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F291" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G291" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H291" s="13" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F291" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G291" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H291" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="I291" s="8"/>
       <c r="J291" s="8"/>
@@ -12203,28 +12197,28 @@
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B292" s="8">
+        <v>29.0</v>
+      </c>
+      <c r="C292" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D292" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B292" s="13">
-        <v>14.0</v>
-      </c>
-      <c r="C292" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D292" s="13" t="s">
-        <v>106</v>
-      </c>
       <c r="E292" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F292" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G292" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H292" s="13" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="F292" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G292" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H292" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="I292" s="8"/>
       <c r="J292" s="8"/>
@@ -12275,28 +12269,28 @@
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B294" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="C294" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D294" s="13" t="s">
-        <v>32</v>
+        <v>28.0</v>
+      </c>
+      <c r="C294" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D294" s="8" t="s">
+        <v>117</v>
       </c>
       <c r="E294" s="13" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="F294" s="13" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G294" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H294" s="13" t="s">
-        <v>69</v>
+        <v>114</v>
+      </c>
+      <c r="H294" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="I294" s="8"/>
       <c r="J294" s="8"/>
@@ -12319,28 +12313,28 @@
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B295" s="8">
+        <v>29.0</v>
+      </c>
+      <c r="C295" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D295" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B295" s="8">
-        <v>6.0</v>
-      </c>
-      <c r="C295" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D295" s="13" t="s">
-        <v>39</v>
-      </c>
       <c r="E295" s="13" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="F295" s="13" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G295" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H295" s="13" t="s">
-        <v>69</v>
+        <v>114</v>
+      </c>
+      <c r="H295" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="I295" s="8"/>
       <c r="J295" s="8"/>
@@ -12362,57 +12356,57 @@
       <c r="Z295" s="9"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="5"/>
-      <c r="B296" s="8"/>
-      <c r="C296" s="8"/>
-      <c r="D296" s="8"/>
-      <c r="E296" s="8"/>
-      <c r="F296" s="8"/>
-      <c r="G296" s="8"/>
-      <c r="H296" s="8"/>
-      <c r="I296" s="8"/>
-      <c r="J296" s="8"/>
-      <c r="K296" s="8"/>
-      <c r="L296" s="8"/>
-      <c r="M296" s="8"/>
-      <c r="N296" s="8"/>
-      <c r="O296" s="8"/>
-      <c r="P296" s="8"/>
-      <c r="Q296" s="8"/>
-      <c r="R296" s="8"/>
-      <c r="S296" s="8"/>
-      <c r="T296" s="8"/>
-      <c r="U296" s="8"/>
-      <c r="V296" s="8"/>
-      <c r="W296" s="8"/>
-      <c r="X296" s="8"/>
-      <c r="Y296" s="8"/>
-      <c r="Z296" s="9"/>
+      <c r="A296" s="15"/>
+      <c r="B296" s="13"/>
+      <c r="C296" s="13"/>
+      <c r="D296" s="13"/>
+      <c r="E296" s="13"/>
+      <c r="F296" s="13"/>
+      <c r="G296" s="13"/>
+      <c r="H296" s="13"/>
+      <c r="I296" s="13"/>
+      <c r="J296" s="13"/>
+      <c r="K296" s="13"/>
+      <c r="L296" s="13"/>
+      <c r="M296" s="13"/>
+      <c r="N296" s="13"/>
+      <c r="O296" s="13"/>
+      <c r="P296" s="13"/>
+      <c r="Q296" s="13"/>
+      <c r="R296" s="13"/>
+      <c r="S296" s="13"/>
+      <c r="T296" s="13"/>
+      <c r="U296" s="13"/>
+      <c r="V296" s="13"/>
+      <c r="W296" s="13"/>
+      <c r="X296" s="13"/>
+      <c r="Y296" s="13"/>
+      <c r="Z296" s="17"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B297" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="C297" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D297" s="13" t="s">
-        <v>20</v>
+        <v>28.0</v>
+      </c>
+      <c r="C297" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D297" s="8" t="s">
+        <v>117</v>
       </c>
       <c r="E297" s="13" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F297" s="13" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G297" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H297" s="13" t="s">
-        <v>73</v>
+        <v>114</v>
+      </c>
+      <c r="H297" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="I297" s="8"/>
       <c r="J297" s="8"/>
@@ -12435,28 +12429,28 @@
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B298" s="8">
+        <v>29.0</v>
+      </c>
+      <c r="C298" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D298" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B298" s="8">
-        <v>6.0</v>
-      </c>
-      <c r="C298" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D298" s="13" t="s">
-        <v>25</v>
-      </c>
       <c r="E298" s="13" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F298" s="13" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G298" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H298" s="13" t="s">
-        <v>73</v>
+        <v>114</v>
+      </c>
+      <c r="H298" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="I298" s="8"/>
       <c r="J298" s="8"/>
@@ -12507,28 +12501,28 @@
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B300" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="C300" s="8" t="s">
-        <v>90</v>
+        <v>119</v>
+      </c>
+      <c r="B300" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="C300" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="D300" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E300" s="8" t="s">
-        <v>76</v>
+        <v>87</v>
+      </c>
+      <c r="E300" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="F300" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G300" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H300" s="8" t="s">
-        <v>76</v>
+        <v>121</v>
+      </c>
+      <c r="H300" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="I300" s="8"/>
       <c r="J300" s="8"/>
@@ -12551,28 +12545,28 @@
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B301" s="8">
-        <v>6.0</v>
-      </c>
-      <c r="C301" s="8" t="s">
-        <v>90</v>
+        <v>119</v>
+      </c>
+      <c r="B301" s="13">
+        <v>14.0</v>
+      </c>
+      <c r="C301" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="D301" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E301" s="8" t="s">
-        <v>76</v>
+        <v>88</v>
+      </c>
+      <c r="E301" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="F301" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G301" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H301" s="8" t="s">
-        <v>76</v>
+        <v>121</v>
+      </c>
+      <c r="H301" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="I301" s="8"/>
       <c r="J301" s="8"/>
@@ -12623,28 +12617,28 @@
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B303" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="C303" s="8" t="s">
-        <v>50</v>
+        <v>119</v>
+      </c>
+      <c r="B303" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="C303" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="D303" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E303" s="8" t="s">
-        <v>51</v>
+        <v>87</v>
+      </c>
+      <c r="E303" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="F303" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G303" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H303" s="8" t="s">
-        <v>51</v>
+        <v>121</v>
+      </c>
+      <c r="H303" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="I303" s="8"/>
       <c r="J303" s="8"/>
@@ -12667,28 +12661,28 @@
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B304" s="8">
-        <v>6.0</v>
-      </c>
-      <c r="C304" s="8" t="s">
-        <v>50</v>
+        <v>119</v>
+      </c>
+      <c r="B304" s="13">
+        <v>14.0</v>
+      </c>
+      <c r="C304" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="D304" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E304" s="8" t="s">
-        <v>51</v>
+        <v>88</v>
+      </c>
+      <c r="E304" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="F304" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G304" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H304" s="8" t="s">
-        <v>51</v>
+        <v>121</v>
+      </c>
+      <c r="H304" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="I304" s="8"/>
       <c r="J304" s="8"/>
@@ -12710,14 +12704,30 @@
       <c r="Z304" s="9"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="5"/>
-      <c r="B305" s="8"/>
-      <c r="C305" s="8"/>
-      <c r="D305" s="8"/>
-      <c r="E305" s="8"/>
-      <c r="F305" s="8"/>
-      <c r="G305" s="8"/>
-      <c r="H305" s="8"/>
+      <c r="A305" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B305" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="C305" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D305" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E305" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F305" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G305" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H305" s="13" t="s">
+        <v>17</v>
+      </c>
       <c r="I305" s="8"/>
       <c r="J305" s="8"/>
       <c r="K305" s="8"/>
@@ -12739,25 +12749,25 @@
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B306" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="C306" s="8" t="s">
-        <v>26</v>
+        <v>119</v>
+      </c>
+      <c r="B306" s="13">
+        <v>14.0</v>
+      </c>
+      <c r="C306" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="D306" s="13" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="E306" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F306" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G306" s="13" t="s">
-        <v>120</v>
+      <c r="F306" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G306" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="H306" s="13" t="s">
         <v>17</v>
@@ -12782,30 +12792,14 @@
       <c r="Z306" s="9"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B307" s="8">
-        <v>6.0</v>
-      </c>
-      <c r="C307" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D307" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E307" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F307" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G307" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H307" s="13" t="s">
-        <v>17</v>
-      </c>
+      <c r="A307" s="5"/>
+      <c r="B307" s="8"/>
+      <c r="C307" s="8"/>
+      <c r="D307" s="8"/>
+      <c r="E307" s="8"/>
+      <c r="F307" s="8"/>
+      <c r="G307" s="8"/>
+      <c r="H307" s="8"/>
       <c r="I307" s="8"/>
       <c r="J307" s="8"/>
       <c r="K307" s="8"/>
@@ -12827,28 +12821,28 @@
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B308" s="8">
         <v>5.0</v>
       </c>
       <c r="C308" s="13" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="D308" s="13" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="E308" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F308" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G308" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="F308" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G308" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="H308" s="13" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="I308" s="8"/>
       <c r="J308" s="8"/>
@@ -12871,28 +12865,28 @@
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B309" s="8">
         <v>6.0</v>
       </c>
       <c r="C309" s="13" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D309" s="13" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="E309" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F309" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G309" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="F309" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G309" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="H309" s="13" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="I309" s="8"/>
       <c r="J309" s="8"/>
@@ -12943,28 +12937,28 @@
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B311" s="8">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="C311" s="13" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="D311" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E311" s="13" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="F311" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G311" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H311" s="13" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="I311" s="8"/>
       <c r="J311" s="8"/>
@@ -12987,28 +12981,28 @@
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B312" s="8">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
       <c r="C312" s="13" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="D312" s="13" t="s">
         <v>25</v>
       </c>
       <c r="E312" s="13" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="F312" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G312" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H312" s="13" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="I312" s="8"/>
       <c r="J312" s="8"/>
@@ -13059,28 +13053,28 @@
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B314" s="8">
-        <v>12.0</v>
-      </c>
-      <c r="C314" s="13" t="s">
-        <v>49</v>
+        <v>5.0</v>
+      </c>
+      <c r="C314" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D314" s="13" t="s">
         <v>32</v>
       </c>
       <c r="E314" s="8" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="F314" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G314" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H314" s="8" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="I314" s="8"/>
       <c r="J314" s="8"/>
@@ -13103,28 +13097,28 @@
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B315" s="8">
-        <v>13.0</v>
-      </c>
-      <c r="C315" s="13" t="s">
-        <v>49</v>
+        <v>6.0</v>
+      </c>
+      <c r="C315" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D315" s="13" t="s">
         <v>39</v>
       </c>
       <c r="E315" s="8" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="F315" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G315" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H315" s="8" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="I315" s="8"/>
       <c r="J315" s="8"/>
@@ -13175,28 +13169,28 @@
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B317" s="8">
-        <v>12.0</v>
-      </c>
-      <c r="C317" s="13" t="s">
-        <v>54</v>
+        <v>5.0</v>
+      </c>
+      <c r="C317" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D317" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E317" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F317" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G317" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H317" s="13" t="s">
-        <v>53</v>
+        <v>32</v>
+      </c>
+      <c r="E317" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F317" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G317" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H317" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="I317" s="8"/>
       <c r="J317" s="8"/>
@@ -13219,28 +13213,28 @@
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B318" s="8">
-        <v>13.0</v>
-      </c>
-      <c r="C318" s="13" t="s">
-        <v>54</v>
+        <v>6.0</v>
+      </c>
+      <c r="C318" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D318" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="E318" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F318" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G318" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H318" s="13" t="s">
-        <v>53</v>
+        <v>39</v>
+      </c>
+      <c r="E318" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F318" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G318" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H318" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="I318" s="8"/>
       <c r="J318" s="8"/>
@@ -13291,28 +13285,28 @@
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B320" s="8">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="C320" s="8" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="D320" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="E320" s="8" t="s">
-        <v>64</v>
+        <v>20</v>
+      </c>
+      <c r="E320" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="F320" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G320" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H320" s="8" t="s">
-        <v>64</v>
+        <v>121</v>
+      </c>
+      <c r="H320" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="I320" s="8"/>
       <c r="J320" s="8"/>
@@ -13335,28 +13329,28 @@
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B321" s="8">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
       <c r="C321" s="8" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="D321" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E321" s="8" t="s">
-        <v>64</v>
+        <v>25</v>
+      </c>
+      <c r="E321" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="F321" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G321" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H321" s="8" t="s">
-        <v>64</v>
+        <v>121</v>
+      </c>
+      <c r="H321" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="I321" s="8"/>
       <c r="J321" s="8"/>
@@ -13379,19 +13373,19 @@
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B322" s="8">
-        <v>12.0</v>
-      </c>
-      <c r="C322" s="8" t="s">
-        <v>65</v>
+        <v>5.0</v>
+      </c>
+      <c r="C322" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="D322" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E322" s="8" t="s">
-        <v>64</v>
+        <v>123</v>
+      </c>
+      <c r="E322" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="F322" s="8" t="s">
         <v>42</v>
@@ -13399,8 +13393,8 @@
       <c r="G322" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H322" s="8" t="s">
-        <v>64</v>
+      <c r="H322" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="I322" s="8"/>
       <c r="J322" s="8"/>
@@ -13423,19 +13417,19 @@
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B323" s="8">
-        <v>13.0</v>
-      </c>
-      <c r="C323" s="8" t="s">
-        <v>65</v>
+        <v>6.0</v>
+      </c>
+      <c r="C323" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="D323" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E323" s="8" t="s">
-        <v>64</v>
+        <v>123</v>
+      </c>
+      <c r="E323" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="F323" s="8" t="s">
         <v>42</v>
@@ -13443,8 +13437,8 @@
       <c r="G323" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H323" s="8" t="s">
-        <v>64</v>
+      <c r="H323" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="I323" s="8"/>
       <c r="J323" s="8"/>
@@ -13495,28 +13489,28 @@
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B325" s="8">
         <v>12.0</v>
       </c>
-      <c r="C325" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D325" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E325" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F325" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G325" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H325" s="8" t="s">
-        <v>60</v>
+      <c r="C325" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D325" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E325" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F325" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G325" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H325" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="I325" s="8"/>
       <c r="J325" s="8"/>
@@ -13539,28 +13533,28 @@
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B326" s="8">
         <v>13.0</v>
       </c>
-      <c r="C326" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D326" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E326" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F326" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G326" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H326" s="8" t="s">
-        <v>60</v>
+      <c r="C326" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D326" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E326" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F326" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G326" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H326" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="I326" s="8"/>
       <c r="J326" s="8"/>
@@ -13611,28 +13605,28 @@
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B328" s="13">
+        <v>119</v>
+      </c>
+      <c r="B328" s="8">
         <v>12.0</v>
       </c>
-      <c r="C328" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D328" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E328" s="13" t="s">
-        <v>11</v>
+      <c r="C328" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D328" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E328" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="F328" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G328" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H328" s="8" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="I328" s="8"/>
       <c r="J328" s="8"/>
@@ -13655,28 +13649,28 @@
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B329" s="13">
+        <v>119</v>
+      </c>
+      <c r="B329" s="8">
         <v>13.0</v>
       </c>
-      <c r="C329" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D329" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E329" s="13" t="s">
-        <v>11</v>
+      <c r="C329" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D329" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E329" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="F329" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G329" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H329" s="8" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="I329" s="8"/>
       <c r="J329" s="8"/>
@@ -13727,27 +13721,27 @@
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B331" s="13">
+        <v>119</v>
+      </c>
+      <c r="B331" s="8">
         <v>12.0</v>
       </c>
-      <c r="C331" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D331" s="15" t="s">
-        <v>10</v>
+      <c r="C331" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D331" s="13" t="s">
+        <v>124</v>
       </c>
       <c r="E331" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F331" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G331" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H331" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F331" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G331" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H331" s="13" t="s">
         <v>53</v>
       </c>
       <c r="I331" s="8"/>
@@ -13771,27 +13765,27 @@
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B332" s="13">
+        <v>119</v>
+      </c>
+      <c r="B332" s="8">
         <v>13.0</v>
       </c>
-      <c r="C332" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D332" s="19" t="s">
-        <v>10</v>
+      <c r="C332" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D332" s="13" t="s">
+        <v>124</v>
       </c>
       <c r="E332" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F332" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="G332" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H332" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F332" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G332" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H332" s="13" t="s">
         <v>53</v>
       </c>
       <c r="I332" s="8"/>
@@ -13842,14 +13836,30 @@
       <c r="Z333" s="9"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="A334" s="5"/>
-      <c r="B334" s="8"/>
-      <c r="C334" s="8"/>
-      <c r="D334" s="8"/>
-      <c r="E334" s="8"/>
-      <c r="F334" s="8"/>
-      <c r="G334" s="8"/>
-      <c r="H334" s="8"/>
+      <c r="A334" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B334" s="8">
+        <v>12.0</v>
+      </c>
+      <c r="C334" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D334" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E334" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F334" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G334" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H334" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="I334" s="8"/>
       <c r="J334" s="8"/>
       <c r="K334" s="8"/>
@@ -13870,14 +13880,30 @@
       <c r="Z334" s="9"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="5"/>
-      <c r="B335" s="8"/>
-      <c r="C335" s="8"/>
-      <c r="D335" s="8"/>
-      <c r="E335" s="8"/>
-      <c r="F335" s="8"/>
-      <c r="G335" s="8"/>
-      <c r="H335" s="8"/>
+      <c r="A335" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B335" s="8">
+        <v>13.0</v>
+      </c>
+      <c r="C335" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D335" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E335" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F335" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G335" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H335" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="I335" s="8"/>
       <c r="J335" s="8"/>
       <c r="K335" s="8"/>
@@ -13898,14 +13924,30 @@
       <c r="Z335" s="9"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="5"/>
-      <c r="B336" s="8"/>
-      <c r="C336" s="8"/>
-      <c r="D336" s="8"/>
-      <c r="E336" s="8"/>
-      <c r="F336" s="8"/>
-      <c r="G336" s="8"/>
-      <c r="H336" s="8"/>
+      <c r="A336" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B336" s="8">
+        <v>12.0</v>
+      </c>
+      <c r="C336" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D336" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E336" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F336" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G336" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H336" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="I336" s="8"/>
       <c r="J336" s="8"/>
       <c r="K336" s="8"/>
@@ -13926,14 +13968,30 @@
       <c r="Z336" s="9"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="5"/>
-      <c r="B337" s="8"/>
-      <c r="C337" s="8"/>
-      <c r="D337" s="8"/>
-      <c r="E337" s="8"/>
-      <c r="F337" s="8"/>
-      <c r="G337" s="8"/>
-      <c r="H337" s="8"/>
+      <c r="A337" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B337" s="8">
+        <v>13.0</v>
+      </c>
+      <c r="C337" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D337" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E337" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F337" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G337" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H337" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="I337" s="8"/>
       <c r="J337" s="8"/>
       <c r="K337" s="8"/>
@@ -13982,14 +14040,30 @@
       <c r="Z338" s="9"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="5"/>
-      <c r="B339" s="8"/>
-      <c r="C339" s="8"/>
-      <c r="D339" s="8"/>
-      <c r="E339" s="8"/>
-      <c r="F339" s="8"/>
-      <c r="G339" s="8"/>
-      <c r="H339" s="8"/>
+      <c r="A339" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B339" s="8">
+        <v>12.0</v>
+      </c>
+      <c r="C339" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D339" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E339" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F339" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G339" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H339" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="I339" s="8"/>
       <c r="J339" s="8"/>
       <c r="K339" s="8"/>
@@ -14010,14 +14084,30 @@
       <c r="Z339" s="9"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="5"/>
-      <c r="B340" s="8"/>
-      <c r="C340" s="8"/>
-      <c r="D340" s="8"/>
-      <c r="E340" s="8"/>
-      <c r="F340" s="8"/>
-      <c r="G340" s="8"/>
-      <c r="H340" s="8"/>
+      <c r="A340" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B340" s="8">
+        <v>13.0</v>
+      </c>
+      <c r="C340" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D340" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E340" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F340" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G340" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H340" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="I340" s="8"/>
       <c r="J340" s="8"/>
       <c r="K340" s="8"/>
@@ -14066,14 +14156,30 @@
       <c r="Z341" s="9"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="5"/>
-      <c r="B342" s="8"/>
-      <c r="C342" s="8"/>
-      <c r="D342" s="8"/>
-      <c r="E342" s="8"/>
-      <c r="F342" s="8"/>
-      <c r="G342" s="8"/>
-      <c r="H342" s="8"/>
+      <c r="A342" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B342" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="C342" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D342" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E342" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F342" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G342" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H342" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="I342" s="8"/>
       <c r="J342" s="8"/>
       <c r="K342" s="8"/>
@@ -14094,14 +14200,30 @@
       <c r="Z342" s="9"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="5"/>
-      <c r="B343" s="8"/>
-      <c r="C343" s="8"/>
-      <c r="D343" s="8"/>
-      <c r="E343" s="8"/>
-      <c r="F343" s="8"/>
-      <c r="G343" s="8"/>
-      <c r="H343" s="8"/>
+      <c r="A343" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B343" s="13">
+        <v>13.0</v>
+      </c>
+      <c r="C343" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D343" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E343" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F343" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G343" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H343" s="8" t="s">
+        <v>60</v>
+      </c>
       <c r="I343" s="8"/>
       <c r="J343" s="8"/>
       <c r="K343" s="8"/>
@@ -14150,14 +14272,30 @@
       <c r="Z344" s="9"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="5"/>
-      <c r="B345" s="8"/>
-      <c r="C345" s="8"/>
-      <c r="D345" s="8"/>
-      <c r="E345" s="8"/>
-      <c r="F345" s="8"/>
-      <c r="G345" s="8"/>
-      <c r="H345" s="8"/>
+      <c r="A345" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B345" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="C345" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D345" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E345" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F345" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G345" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H345" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="I345" s="8"/>
       <c r="J345" s="8"/>
       <c r="K345" s="8"/>
@@ -14178,14 +14316,30 @@
       <c r="Z345" s="9"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="A346" s="5"/>
-      <c r="B346" s="8"/>
-      <c r="C346" s="8"/>
-      <c r="D346" s="8"/>
-      <c r="E346" s="8"/>
-      <c r="F346" s="8"/>
-      <c r="G346" s="8"/>
-      <c r="H346" s="8"/>
+      <c r="A346" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B346" s="13">
+        <v>13.0</v>
+      </c>
+      <c r="C346" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D346" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E346" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F346" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G346" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H346" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="I346" s="8"/>
       <c r="J346" s="8"/>
       <c r="K346" s="8"/>
@@ -14234,60 +14388,92 @@
       <c r="Z347" s="9"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="5"/>
-      <c r="B348" s="8"/>
-      <c r="C348" s="8"/>
-      <c r="D348" s="8"/>
-      <c r="E348" s="8"/>
-      <c r="F348" s="8"/>
-      <c r="G348" s="8"/>
-      <c r="H348" s="8"/>
-      <c r="I348" s="8"/>
-      <c r="J348" s="8"/>
-      <c r="K348" s="8"/>
-      <c r="L348" s="8"/>
-      <c r="M348" s="8"/>
-      <c r="N348" s="8"/>
-      <c r="O348" s="8"/>
-      <c r="P348" s="8"/>
-      <c r="Q348" s="8"/>
-      <c r="R348" s="8"/>
-      <c r="S348" s="8"/>
-      <c r="T348" s="8"/>
-      <c r="U348" s="8"/>
-      <c r="V348" s="8"/>
-      <c r="W348" s="8"/>
-      <c r="X348" s="8"/>
-      <c r="Y348" s="8"/>
-      <c r="Z348" s="9"/>
+      <c r="A348" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B348" s="23">
+        <v>12.0</v>
+      </c>
+      <c r="C348" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D348" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E348" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F348" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="G348" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="H348" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I348" s="24"/>
+      <c r="J348" s="24"/>
+      <c r="K348" s="24"/>
+      <c r="L348" s="24"/>
+      <c r="M348" s="24"/>
+      <c r="N348" s="24"/>
+      <c r="O348" s="24"/>
+      <c r="P348" s="24"/>
+      <c r="Q348" s="24"/>
+      <c r="R348" s="24"/>
+      <c r="S348" s="24"/>
+      <c r="T348" s="24"/>
+      <c r="U348" s="24"/>
+      <c r="V348" s="24"/>
+      <c r="W348" s="24"/>
+      <c r="X348" s="24"/>
+      <c r="Y348" s="24"/>
+      <c r="Z348" s="25"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="5"/>
-      <c r="B349" s="8"/>
-      <c r="C349" s="8"/>
-      <c r="D349" s="8"/>
-      <c r="E349" s="8"/>
-      <c r="F349" s="8"/>
-      <c r="G349" s="8"/>
-      <c r="H349" s="8"/>
-      <c r="I349" s="8"/>
-      <c r="J349" s="8"/>
-      <c r="K349" s="8"/>
-      <c r="L349" s="8"/>
-      <c r="M349" s="8"/>
-      <c r="N349" s="8"/>
-      <c r="O349" s="8"/>
-      <c r="P349" s="8"/>
-      <c r="Q349" s="8"/>
-      <c r="R349" s="8"/>
-      <c r="S349" s="8"/>
-      <c r="T349" s="8"/>
-      <c r="U349" s="8"/>
-      <c r="V349" s="8"/>
-      <c r="W349" s="8"/>
-      <c r="X349" s="8"/>
-      <c r="Y349" s="8"/>
-      <c r="Z349" s="9"/>
+      <c r="A349" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B349" s="23">
+        <v>13.0</v>
+      </c>
+      <c r="C349" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D349" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E349" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F349" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="G349" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="H349" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I349" s="24"/>
+      <c r="J349" s="24"/>
+      <c r="K349" s="24"/>
+      <c r="L349" s="24"/>
+      <c r="M349" s="24"/>
+      <c r="N349" s="24"/>
+      <c r="O349" s="24"/>
+      <c r="P349" s="24"/>
+      <c r="Q349" s="24"/>
+      <c r="R349" s="24"/>
+      <c r="S349" s="24"/>
+      <c r="T349" s="24"/>
+      <c r="U349" s="24"/>
+      <c r="V349" s="24"/>
+      <c r="W349" s="24"/>
+      <c r="X349" s="24"/>
+      <c r="Y349" s="24"/>
+      <c r="Z349" s="25"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="5"/>
@@ -19413,20 +19599,398 @@
       <c r="Y532" s="8"/>
       <c r="Z532" s="9"/>
     </row>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1">
+      <c r="A533" s="5"/>
+      <c r="B533" s="8"/>
+      <c r="C533" s="8"/>
+      <c r="D533" s="8"/>
+      <c r="E533" s="8"/>
+      <c r="F533" s="8"/>
+      <c r="G533" s="8"/>
+      <c r="H533" s="8"/>
+      <c r="I533" s="8"/>
+      <c r="J533" s="8"/>
+      <c r="K533" s="8"/>
+      <c r="L533" s="8"/>
+      <c r="M533" s="8"/>
+      <c r="N533" s="8"/>
+      <c r="O533" s="8"/>
+      <c r="P533" s="8"/>
+      <c r="Q533" s="8"/>
+      <c r="R533" s="8"/>
+      <c r="S533" s="8"/>
+      <c r="T533" s="8"/>
+      <c r="U533" s="8"/>
+      <c r="V533" s="8"/>
+      <c r="W533" s="8"/>
+      <c r="X533" s="8"/>
+      <c r="Y533" s="8"/>
+      <c r="Z533" s="9"/>
+    </row>
+    <row r="534" ht="15.75" customHeight="1">
+      <c r="A534" s="5"/>
+      <c r="B534" s="8"/>
+      <c r="C534" s="8"/>
+      <c r="D534" s="8"/>
+      <c r="E534" s="8"/>
+      <c r="F534" s="8"/>
+      <c r="G534" s="8"/>
+      <c r="H534" s="8"/>
+      <c r="I534" s="8"/>
+      <c r="J534" s="8"/>
+      <c r="K534" s="8"/>
+      <c r="L534" s="8"/>
+      <c r="M534" s="8"/>
+      <c r="N534" s="8"/>
+      <c r="O534" s="8"/>
+      <c r="P534" s="8"/>
+      <c r="Q534" s="8"/>
+      <c r="R534" s="8"/>
+      <c r="S534" s="8"/>
+      <c r="T534" s="8"/>
+      <c r="U534" s="8"/>
+      <c r="V534" s="8"/>
+      <c r="W534" s="8"/>
+      <c r="X534" s="8"/>
+      <c r="Y534" s="8"/>
+      <c r="Z534" s="9"/>
+    </row>
+    <row r="535" ht="15.75" customHeight="1">
+      <c r="A535" s="5"/>
+      <c r="B535" s="8"/>
+      <c r="C535" s="8"/>
+      <c r="D535" s="8"/>
+      <c r="E535" s="8"/>
+      <c r="F535" s="8"/>
+      <c r="G535" s="8"/>
+      <c r="H535" s="8"/>
+      <c r="I535" s="8"/>
+      <c r="J535" s="8"/>
+      <c r="K535" s="8"/>
+      <c r="L535" s="8"/>
+      <c r="M535" s="8"/>
+      <c r="N535" s="8"/>
+      <c r="O535" s="8"/>
+      <c r="P535" s="8"/>
+      <c r="Q535" s="8"/>
+      <c r="R535" s="8"/>
+      <c r="S535" s="8"/>
+      <c r="T535" s="8"/>
+      <c r="U535" s="8"/>
+      <c r="V535" s="8"/>
+      <c r="W535" s="8"/>
+      <c r="X535" s="8"/>
+      <c r="Y535" s="8"/>
+      <c r="Z535" s="9"/>
+    </row>
+    <row r="536" ht="15.75" customHeight="1">
+      <c r="A536" s="5"/>
+      <c r="B536" s="8"/>
+      <c r="C536" s="8"/>
+      <c r="D536" s="8"/>
+      <c r="E536" s="8"/>
+      <c r="F536" s="8"/>
+      <c r="G536" s="8"/>
+      <c r="H536" s="8"/>
+      <c r="I536" s="8"/>
+      <c r="J536" s="8"/>
+      <c r="K536" s="8"/>
+      <c r="L536" s="8"/>
+      <c r="M536" s="8"/>
+      <c r="N536" s="8"/>
+      <c r="O536" s="8"/>
+      <c r="P536" s="8"/>
+      <c r="Q536" s="8"/>
+      <c r="R536" s="8"/>
+      <c r="S536" s="8"/>
+      <c r="T536" s="8"/>
+      <c r="U536" s="8"/>
+      <c r="V536" s="8"/>
+      <c r="W536" s="8"/>
+      <c r="X536" s="8"/>
+      <c r="Y536" s="8"/>
+      <c r="Z536" s="9"/>
+    </row>
+    <row r="537" ht="15.75" customHeight="1">
+      <c r="A537" s="5"/>
+      <c r="B537" s="8"/>
+      <c r="C537" s="8"/>
+      <c r="D537" s="8"/>
+      <c r="E537" s="8"/>
+      <c r="F537" s="8"/>
+      <c r="G537" s="8"/>
+      <c r="H537" s="8"/>
+      <c r="I537" s="8"/>
+      <c r="J537" s="8"/>
+      <c r="K537" s="8"/>
+      <c r="L537" s="8"/>
+      <c r="M537" s="8"/>
+      <c r="N537" s="8"/>
+      <c r="O537" s="8"/>
+      <c r="P537" s="8"/>
+      <c r="Q537" s="8"/>
+      <c r="R537" s="8"/>
+      <c r="S537" s="8"/>
+      <c r="T537" s="8"/>
+      <c r="U537" s="8"/>
+      <c r="V537" s="8"/>
+      <c r="W537" s="8"/>
+      <c r="X537" s="8"/>
+      <c r="Y537" s="8"/>
+      <c r="Z537" s="9"/>
+    </row>
+    <row r="538" ht="15.75" customHeight="1">
+      <c r="A538" s="5"/>
+      <c r="B538" s="8"/>
+      <c r="C538" s="8"/>
+      <c r="D538" s="8"/>
+      <c r="E538" s="8"/>
+      <c r="F538" s="8"/>
+      <c r="G538" s="8"/>
+      <c r="H538" s="8"/>
+      <c r="I538" s="8"/>
+      <c r="J538" s="8"/>
+      <c r="K538" s="8"/>
+      <c r="L538" s="8"/>
+      <c r="M538" s="8"/>
+      <c r="N538" s="8"/>
+      <c r="O538" s="8"/>
+      <c r="P538" s="8"/>
+      <c r="Q538" s="8"/>
+      <c r="R538" s="8"/>
+      <c r="S538" s="8"/>
+      <c r="T538" s="8"/>
+      <c r="U538" s="8"/>
+      <c r="V538" s="8"/>
+      <c r="W538" s="8"/>
+      <c r="X538" s="8"/>
+      <c r="Y538" s="8"/>
+      <c r="Z538" s="9"/>
+    </row>
+    <row r="539" ht="15.75" customHeight="1">
+      <c r="A539" s="5"/>
+      <c r="B539" s="8"/>
+      <c r="C539" s="8"/>
+      <c r="D539" s="8"/>
+      <c r="E539" s="8"/>
+      <c r="F539" s="8"/>
+      <c r="G539" s="8"/>
+      <c r="H539" s="8"/>
+      <c r="I539" s="8"/>
+      <c r="J539" s="8"/>
+      <c r="K539" s="8"/>
+      <c r="L539" s="8"/>
+      <c r="M539" s="8"/>
+      <c r="N539" s="8"/>
+      <c r="O539" s="8"/>
+      <c r="P539" s="8"/>
+      <c r="Q539" s="8"/>
+      <c r="R539" s="8"/>
+      <c r="S539" s="8"/>
+      <c r="T539" s="8"/>
+      <c r="U539" s="8"/>
+      <c r="V539" s="8"/>
+      <c r="W539" s="8"/>
+      <c r="X539" s="8"/>
+      <c r="Y539" s="8"/>
+      <c r="Z539" s="9"/>
+    </row>
+    <row r="540" ht="15.75" customHeight="1">
+      <c r="A540" s="5"/>
+      <c r="B540" s="8"/>
+      <c r="C540" s="8"/>
+      <c r="D540" s="8"/>
+      <c r="E540" s="8"/>
+      <c r="F540" s="8"/>
+      <c r="G540" s="8"/>
+      <c r="H540" s="8"/>
+      <c r="I540" s="8"/>
+      <c r="J540" s="8"/>
+      <c r="K540" s="8"/>
+      <c r="L540" s="8"/>
+      <c r="M540" s="8"/>
+      <c r="N540" s="8"/>
+      <c r="O540" s="8"/>
+      <c r="P540" s="8"/>
+      <c r="Q540" s="8"/>
+      <c r="R540" s="8"/>
+      <c r="S540" s="8"/>
+      <c r="T540" s="8"/>
+      <c r="U540" s="8"/>
+      <c r="V540" s="8"/>
+      <c r="W540" s="8"/>
+      <c r="X540" s="8"/>
+      <c r="Y540" s="8"/>
+      <c r="Z540" s="9"/>
+    </row>
+    <row r="541" ht="15.75" customHeight="1">
+      <c r="A541" s="5"/>
+      <c r="B541" s="8"/>
+      <c r="C541" s="8"/>
+      <c r="D541" s="8"/>
+      <c r="E541" s="8"/>
+      <c r="F541" s="8"/>
+      <c r="G541" s="8"/>
+      <c r="H541" s="8"/>
+      <c r="I541" s="8"/>
+      <c r="J541" s="8"/>
+      <c r="K541" s="8"/>
+      <c r="L541" s="8"/>
+      <c r="M541" s="8"/>
+      <c r="N541" s="8"/>
+      <c r="O541" s="8"/>
+      <c r="P541" s="8"/>
+      <c r="Q541" s="8"/>
+      <c r="R541" s="8"/>
+      <c r="S541" s="8"/>
+      <c r="T541" s="8"/>
+      <c r="U541" s="8"/>
+      <c r="V541" s="8"/>
+      <c r="W541" s="8"/>
+      <c r="X541" s="8"/>
+      <c r="Y541" s="8"/>
+      <c r="Z541" s="9"/>
+    </row>
+    <row r="542" ht="15.75" customHeight="1">
+      <c r="A542" s="5"/>
+      <c r="B542" s="8"/>
+      <c r="C542" s="8"/>
+      <c r="D542" s="8"/>
+      <c r="E542" s="8"/>
+      <c r="F542" s="8"/>
+      <c r="G542" s="8"/>
+      <c r="H542" s="8"/>
+      <c r="I542" s="8"/>
+      <c r="J542" s="8"/>
+      <c r="K542" s="8"/>
+      <c r="L542" s="8"/>
+      <c r="M542" s="8"/>
+      <c r="N542" s="8"/>
+      <c r="O542" s="8"/>
+      <c r="P542" s="8"/>
+      <c r="Q542" s="8"/>
+      <c r="R542" s="8"/>
+      <c r="S542" s="8"/>
+      <c r="T542" s="8"/>
+      <c r="U542" s="8"/>
+      <c r="V542" s="8"/>
+      <c r="W542" s="8"/>
+      <c r="X542" s="8"/>
+      <c r="Y542" s="8"/>
+      <c r="Z542" s="9"/>
+    </row>
+    <row r="543" ht="15.75" customHeight="1">
+      <c r="A543" s="5"/>
+      <c r="B543" s="8"/>
+      <c r="C543" s="8"/>
+      <c r="D543" s="8"/>
+      <c r="E543" s="8"/>
+      <c r="F543" s="8"/>
+      <c r="G543" s="8"/>
+      <c r="H543" s="8"/>
+      <c r="I543" s="8"/>
+      <c r="J543" s="8"/>
+      <c r="K543" s="8"/>
+      <c r="L543" s="8"/>
+      <c r="M543" s="8"/>
+      <c r="N543" s="8"/>
+      <c r="O543" s="8"/>
+      <c r="P543" s="8"/>
+      <c r="Q543" s="8"/>
+      <c r="R543" s="8"/>
+      <c r="S543" s="8"/>
+      <c r="T543" s="8"/>
+      <c r="U543" s="8"/>
+      <c r="V543" s="8"/>
+      <c r="W543" s="8"/>
+      <c r="X543" s="8"/>
+      <c r="Y543" s="8"/>
+      <c r="Z543" s="9"/>
+    </row>
+    <row r="544" ht="15.75" customHeight="1">
+      <c r="A544" s="5"/>
+      <c r="B544" s="8"/>
+      <c r="C544" s="8"/>
+      <c r="D544" s="8"/>
+      <c r="E544" s="8"/>
+      <c r="F544" s="8"/>
+      <c r="G544" s="8"/>
+      <c r="H544" s="8"/>
+      <c r="I544" s="8"/>
+      <c r="J544" s="8"/>
+      <c r="K544" s="8"/>
+      <c r="L544" s="8"/>
+      <c r="M544" s="8"/>
+      <c r="N544" s="8"/>
+      <c r="O544" s="8"/>
+      <c r="P544" s="8"/>
+      <c r="Q544" s="8"/>
+      <c r="R544" s="8"/>
+      <c r="S544" s="8"/>
+      <c r="T544" s="8"/>
+      <c r="U544" s="8"/>
+      <c r="V544" s="8"/>
+      <c r="W544" s="8"/>
+      <c r="X544" s="8"/>
+      <c r="Y544" s="8"/>
+      <c r="Z544" s="9"/>
+    </row>
+    <row r="545" ht="15.75" customHeight="1">
+      <c r="A545" s="5"/>
+      <c r="B545" s="8"/>
+      <c r="C545" s="8"/>
+      <c r="D545" s="8"/>
+      <c r="E545" s="8"/>
+      <c r="F545" s="8"/>
+      <c r="G545" s="8"/>
+      <c r="H545" s="8"/>
+      <c r="I545" s="8"/>
+      <c r="J545" s="8"/>
+      <c r="K545" s="8"/>
+      <c r="L545" s="8"/>
+      <c r="M545" s="8"/>
+      <c r="N545" s="8"/>
+      <c r="O545" s="8"/>
+      <c r="P545" s="8"/>
+      <c r="Q545" s="8"/>
+      <c r="R545" s="8"/>
+      <c r="S545" s="8"/>
+      <c r="T545" s="8"/>
+      <c r="U545" s="8"/>
+      <c r="V545" s="8"/>
+      <c r="W545" s="8"/>
+      <c r="X545" s="8"/>
+      <c r="Y545" s="8"/>
+      <c r="Z545" s="9"/>
+    </row>
+    <row r="546" ht="15.75" customHeight="1">
+      <c r="A546" s="5"/>
+      <c r="B546" s="8"/>
+      <c r="C546" s="8"/>
+      <c r="D546" s="8"/>
+      <c r="E546" s="8"/>
+      <c r="F546" s="8"/>
+      <c r="G546" s="8"/>
+      <c r="H546" s="8"/>
+      <c r="I546" s="8"/>
+      <c r="J546" s="8"/>
+      <c r="K546" s="8"/>
+      <c r="L546" s="8"/>
+      <c r="M546" s="8"/>
+      <c r="N546" s="8"/>
+      <c r="O546" s="8"/>
+      <c r="P546" s="8"/>
+      <c r="Q546" s="8"/>
+      <c r="R546" s="8"/>
+      <c r="S546" s="8"/>
+      <c r="T546" s="8"/>
+      <c r="U546" s="8"/>
+      <c r="V546" s="8"/>
+      <c r="W546" s="8"/>
+      <c r="X546" s="8"/>
+      <c r="Y546" s="8"/>
+      <c r="Z546" s="9"/>
+    </row>
     <row r="547" ht="15.75" customHeight="1"/>
     <row r="548" ht="15.75" customHeight="1"/>
     <row r="549" ht="15.75" customHeight="1"/>
@@ -19881,6 +20445,20 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Prática Clínica - Preenchimento Facial</t>
   </si>
   <si>
-    <t xml:space="preserve">Paulista</t>
+    <t xml:space="preserve">São Paulo</t>
   </si>
   <si>
     <t xml:space="preserve">Prática Clinica        </t>
